--- a/packages/server/src/arpa_reporter/data/treasury/projectBaselineBulkUploadTemplate.xlsx
+++ b/packages/server/src/arpa_reporter/data/treasury/projectBaselineBulkUploadTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JohnsonTa\Desktop\SLFRF Templates\SLFRF Q2 2026 Updates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Projects\arpa-reporter\packages\server\src\arpa_reporter\data\treasury\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F438CB-25A3-4F9B-8C8D-B34BECBAA564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353FF1C8-505C-4FDF-A35F-16AF150C8EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="90" windowWidth="28800" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1545" windowWidth="22747" windowHeight="12277" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline" sheetId="1" r:id="rId1"/>
@@ -592,10 +592,10 @@
 "No"</t>
   </si>
   <si>
-    <t>Q2_2026_Obligations__c</t>
+    <t>Q3_2026_Obligations__c</t>
   </si>
   <si>
-    <t>Q2_2026_Expenditures__c</t>
+    <t>Q3_2026_Expenditures__c</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1019,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AM1000"/>
-  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="53" style="4" customWidth="1"/>
     <col min="2" max="20" width="35.5" style="4" customWidth="1"/>
@@ -1031,7 +1031,7 @@
     <col min="40" max="16384" width="12.5" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>80</v>
       </c>
@@ -1074,7 +1074,7 @@
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
     </row>
-    <row r="2" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
@@ -1117,7 +1117,7 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:39" ht="210" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" ht="210" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>35</v>
       </c>
@@ -1160,7 +1160,7 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="51.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" ht="51.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="51" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" ht="51" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>29</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:39" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1677,7 +1677,7 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
     </row>
-    <row r="9" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1718,7 +1718,7 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
     </row>
-    <row r="10" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1759,7 +1759,7 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
     </row>
-    <row r="11" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1800,7 +1800,7 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1841,7 +1841,7 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1882,7 +1882,7 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
     </row>
-    <row r="14" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1923,7 +1923,7 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
     </row>
-    <row r="15" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1964,7 +1964,7 @@
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
     </row>
-    <row r="16" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2005,7 +2005,7 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2046,7 +2046,7 @@
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
     </row>
-    <row r="18" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2087,7 +2087,7 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
     </row>
-    <row r="19" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:39" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2128,7 +2128,7 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2169,7 +2169,7 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
     </row>
-    <row r="21" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2210,7 +2210,7 @@
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
     </row>
-    <row r="22" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2251,7 +2251,7 @@
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
     </row>
-    <row r="23" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2292,7 +2292,7 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2333,7 +2333,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2374,7 +2374,7 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2415,7 +2415,7 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2456,7 +2456,7 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
     </row>
-    <row r="28" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2497,7 +2497,7 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
     </row>
-    <row r="29" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2538,7 +2538,7 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
     </row>
-    <row r="30" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2579,7 +2579,7 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
     </row>
-    <row r="31" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2620,7 +2620,7 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
     </row>
-    <row r="32" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2661,7 +2661,7 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
     </row>
-    <row r="33" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2702,7 +2702,7 @@
       <c r="AL33" s="3"/>
       <c r="AM33" s="3"/>
     </row>
-    <row r="34" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2743,7 +2743,7 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
     </row>
-    <row r="35" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2784,7 +2784,7 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2825,7 +2825,7 @@
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2866,7 +2866,7 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2907,7 +2907,7 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2948,7 +2948,7 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2989,7 +2989,7 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -3030,7 +3030,7 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -3071,7 +3071,7 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -3112,7 +3112,7 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -3153,7 +3153,7 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -3194,7 +3194,7 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -3235,7 +3235,7 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -3276,7 +3276,7 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -3317,7 +3317,7 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -3358,7 +3358,7 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -3399,7 +3399,7 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -3440,7 +3440,7 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -3481,7 +3481,7 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -3522,7 +3522,7 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -3563,7 +3563,7 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3604,7 +3604,7 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3645,7 +3645,7 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3686,7 +3686,7 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -3727,7 +3727,7 @@
       <c r="AL58" s="3"/>
       <c r="AM58" s="3"/>
     </row>
-    <row r="59" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -3768,7 +3768,7 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
     </row>
-    <row r="60" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3809,7 +3809,7 @@
       <c r="AL60" s="3"/>
       <c r="AM60" s="3"/>
     </row>
-    <row r="61" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3850,7 +3850,7 @@
       <c r="AL61" s="3"/>
       <c r="AM61" s="3"/>
     </row>
-    <row r="62" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3891,7 +3891,7 @@
       <c r="AL62" s="3"/>
       <c r="AM62" s="3"/>
     </row>
-    <row r="63" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3932,7 +3932,7 @@
       <c r="AL63" s="3"/>
       <c r="AM63" s="3"/>
     </row>
-    <row r="64" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3973,7 +3973,7 @@
       <c r="AL64" s="3"/>
       <c r="AM64" s="3"/>
     </row>
-    <row r="65" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -4014,7 +4014,7 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
     </row>
-    <row r="66" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -4055,7 +4055,7 @@
       <c r="AL66" s="3"/>
       <c r="AM66" s="3"/>
     </row>
-    <row r="67" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -4096,7 +4096,7 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -4137,7 +4137,7 @@
       <c r="AL68" s="3"/>
       <c r="AM68" s="3"/>
     </row>
-    <row r="69" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -4178,7 +4178,7 @@
       <c r="AL69" s="3"/>
       <c r="AM69" s="3"/>
     </row>
-    <row r="70" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -4219,7 +4219,7 @@
       <c r="AL70" s="3"/>
       <c r="AM70" s="3"/>
     </row>
-    <row r="71" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -4260,7 +4260,7 @@
       <c r="AL71" s="3"/>
       <c r="AM71" s="3"/>
     </row>
-    <row r="72" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -4301,7 +4301,7 @@
       <c r="AL72" s="3"/>
       <c r="AM72" s="3"/>
     </row>
-    <row r="73" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -4342,7 +4342,7 @@
       <c r="AL73" s="3"/>
       <c r="AM73" s="3"/>
     </row>
-    <row r="74" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -4383,7 +4383,7 @@
       <c r="AL74" s="3"/>
       <c r="AM74" s="3"/>
     </row>
-    <row r="75" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -4424,7 +4424,7 @@
       <c r="AL75" s="3"/>
       <c r="AM75" s="3"/>
     </row>
-    <row r="76" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -4465,7 +4465,7 @@
       <c r="AL76" s="3"/>
       <c r="AM76" s="3"/>
     </row>
-    <row r="77" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -4506,7 +4506,7 @@
       <c r="AL77" s="3"/>
       <c r="AM77" s="3"/>
     </row>
-    <row r="78" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -4547,7 +4547,7 @@
       <c r="AL78" s="3"/>
       <c r="AM78" s="3"/>
     </row>
-    <row r="79" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -4588,7 +4588,7 @@
       <c r="AL79" s="3"/>
       <c r="AM79" s="3"/>
     </row>
-    <row r="80" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -4629,7 +4629,7 @@
       <c r="AL80" s="3"/>
       <c r="AM80" s="3"/>
     </row>
-    <row r="81" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -4670,7 +4670,7 @@
       <c r="AL81" s="3"/>
       <c r="AM81" s="3"/>
     </row>
-    <row r="82" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -4711,7 +4711,7 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -4752,7 +4752,7 @@
       <c r="AL83" s="3"/>
       <c r="AM83" s="3"/>
     </row>
-    <row r="84" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -4793,7 +4793,7 @@
       <c r="AL84" s="3"/>
       <c r="AM84" s="3"/>
     </row>
-    <row r="85" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -4834,7 +4834,7 @@
       <c r="AL85" s="3"/>
       <c r="AM85" s="3"/>
     </row>
-    <row r="86" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -4875,7 +4875,7 @@
       <c r="AL86" s="3"/>
       <c r="AM86" s="3"/>
     </row>
-    <row r="87" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -4916,7 +4916,7 @@
       <c r="AL87" s="3"/>
       <c r="AM87" s="3"/>
     </row>
-    <row r="88" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -4957,7 +4957,7 @@
       <c r="AL88" s="3"/>
       <c r="AM88" s="3"/>
     </row>
-    <row r="89" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -4998,7 +4998,7 @@
       <c r="AL89" s="3"/>
       <c r="AM89" s="3"/>
     </row>
-    <row r="90" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -5039,7 +5039,7 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -5080,7 +5080,7 @@
       <c r="AL91" s="3"/>
       <c r="AM91" s="3"/>
     </row>
-    <row r="92" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -5121,7 +5121,7 @@
       <c r="AL92" s="3"/>
       <c r="AM92" s="3"/>
     </row>
-    <row r="93" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -5162,7 +5162,7 @@
       <c r="AL93" s="3"/>
       <c r="AM93" s="3"/>
     </row>
-    <row r="94" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -5203,7 +5203,7 @@
       <c r="AL94" s="3"/>
       <c r="AM94" s="3"/>
     </row>
-    <row r="95" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -5244,7 +5244,7 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -5285,7 +5285,7 @@
       <c r="AL96" s="3"/>
       <c r="AM96" s="3"/>
     </row>
-    <row r="97" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -5326,7 +5326,7 @@
       <c r="AL97" s="3"/>
       <c r="AM97" s="3"/>
     </row>
-    <row r="98" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -5367,7 +5367,7 @@
       <c r="AL98" s="3"/>
       <c r="AM98" s="3"/>
     </row>
-    <row r="99" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -5408,7 +5408,7 @@
       <c r="AL99" s="3"/>
       <c r="AM99" s="3"/>
     </row>
-    <row r="100" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -5449,7 +5449,7 @@
       <c r="AL100" s="3"/>
       <c r="AM100" s="3"/>
     </row>
-    <row r="101" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -5490,7 +5490,7 @@
       <c r="AL101" s="3"/>
       <c r="AM101" s="3"/>
     </row>
-    <row r="102" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -5531,7 +5531,7 @@
       <c r="AL102" s="3"/>
       <c r="AM102" s="3"/>
     </row>
-    <row r="103" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -5572,7 +5572,7 @@
       <c r="AL103" s="3"/>
       <c r="AM103" s="3"/>
     </row>
-    <row r="104" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -5613,7 +5613,7 @@
       <c r="AL104" s="3"/>
       <c r="AM104" s="3"/>
     </row>
-    <row r="105" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -5654,7 +5654,7 @@
       <c r="AL105" s="3"/>
       <c r="AM105" s="3"/>
     </row>
-    <row r="106" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -5695,7 +5695,7 @@
       <c r="AL106" s="3"/>
       <c r="AM106" s="3"/>
     </row>
-    <row r="107" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -5736,7 +5736,7 @@
       <c r="AL107" s="3"/>
       <c r="AM107" s="3"/>
     </row>
-    <row r="108" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -5777,7 +5777,7 @@
       <c r="AL108" s="3"/>
       <c r="AM108" s="3"/>
     </row>
-    <row r="109" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -5818,7 +5818,7 @@
       <c r="AL109" s="3"/>
       <c r="AM109" s="3"/>
     </row>
-    <row r="110" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -5859,7 +5859,7 @@
       <c r="AL110" s="3"/>
       <c r="AM110" s="3"/>
     </row>
-    <row r="111" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -5900,7 +5900,7 @@
       <c r="AL111" s="3"/>
       <c r="AM111" s="3"/>
     </row>
-    <row r="112" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -5941,7 +5941,7 @@
       <c r="AL112" s="3"/>
       <c r="AM112" s="3"/>
     </row>
-    <row r="113" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -5982,7 +5982,7 @@
       <c r="AL113" s="3"/>
       <c r="AM113" s="3"/>
     </row>
-    <row r="114" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -6023,7 +6023,7 @@
       <c r="AL114" s="3"/>
       <c r="AM114" s="3"/>
     </row>
-    <row r="115" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -6064,7 +6064,7 @@
       <c r="AL115" s="3"/>
       <c r="AM115" s="3"/>
     </row>
-    <row r="116" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -6105,7 +6105,7 @@
       <c r="AL116" s="3"/>
       <c r="AM116" s="3"/>
     </row>
-    <row r="117" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -6146,7 +6146,7 @@
       <c r="AL117" s="3"/>
       <c r="AM117" s="3"/>
     </row>
-    <row r="118" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -6187,7 +6187,7 @@
       <c r="AL118" s="3"/>
       <c r="AM118" s="3"/>
     </row>
-    <row r="119" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -6228,7 +6228,7 @@
       <c r="AL119" s="3"/>
       <c r="AM119" s="3"/>
     </row>
-    <row r="120" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -6269,7 +6269,7 @@
       <c r="AL120" s="3"/>
       <c r="AM120" s="3"/>
     </row>
-    <row r="121" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -6310,7 +6310,7 @@
       <c r="AL121" s="3"/>
       <c r="AM121" s="3"/>
     </row>
-    <row r="122" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -6351,7 +6351,7 @@
       <c r="AL122" s="3"/>
       <c r="AM122" s="3"/>
     </row>
-    <row r="123" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -6392,7 +6392,7 @@
       <c r="AL123" s="3"/>
       <c r="AM123" s="3"/>
     </row>
-    <row r="124" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -6433,7 +6433,7 @@
       <c r="AL124" s="3"/>
       <c r="AM124" s="3"/>
     </row>
-    <row r="125" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -6474,7 +6474,7 @@
       <c r="AL125" s="3"/>
       <c r="AM125" s="3"/>
     </row>
-    <row r="126" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -6515,7 +6515,7 @@
       <c r="AL126" s="3"/>
       <c r="AM126" s="3"/>
     </row>
-    <row r="127" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -6556,7 +6556,7 @@
       <c r="AL127" s="3"/>
       <c r="AM127" s="3"/>
     </row>
-    <row r="128" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -6597,7 +6597,7 @@
       <c r="AL128" s="3"/>
       <c r="AM128" s="3"/>
     </row>
-    <row r="129" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -6638,7 +6638,7 @@
       <c r="AL129" s="3"/>
       <c r="AM129" s="3"/>
     </row>
-    <row r="130" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -6679,7 +6679,7 @@
       <c r="AL130" s="3"/>
       <c r="AM130" s="3"/>
     </row>
-    <row r="131" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -6720,7 +6720,7 @@
       <c r="AL131" s="3"/>
       <c r="AM131" s="3"/>
     </row>
-    <row r="132" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -6761,7 +6761,7 @@
       <c r="AL132" s="3"/>
       <c r="AM132" s="3"/>
     </row>
-    <row r="133" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -6802,7 +6802,7 @@
       <c r="AL133" s="3"/>
       <c r="AM133" s="3"/>
     </row>
-    <row r="134" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -6843,7 +6843,7 @@
       <c r="AL134" s="3"/>
       <c r="AM134" s="3"/>
     </row>
-    <row r="135" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -6884,7 +6884,7 @@
       <c r="AL135" s="3"/>
       <c r="AM135" s="3"/>
     </row>
-    <row r="136" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -6925,7 +6925,7 @@
       <c r="AL136" s="3"/>
       <c r="AM136" s="3"/>
     </row>
-    <row r="137" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -6966,7 +6966,7 @@
       <c r="AL137" s="3"/>
       <c r="AM137" s="3"/>
     </row>
-    <row r="138" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -7007,7 +7007,7 @@
       <c r="AL138" s="3"/>
       <c r="AM138" s="3"/>
     </row>
-    <row r="139" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -7048,7 +7048,7 @@
       <c r="AL139" s="3"/>
       <c r="AM139" s="3"/>
     </row>
-    <row r="140" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -7089,7 +7089,7 @@
       <c r="AL140" s="3"/>
       <c r="AM140" s="3"/>
     </row>
-    <row r="141" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -7130,7 +7130,7 @@
       <c r="AL141" s="3"/>
       <c r="AM141" s="3"/>
     </row>
-    <row r="142" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -7171,7 +7171,7 @@
       <c r="AL142" s="3"/>
       <c r="AM142" s="3"/>
     </row>
-    <row r="143" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -7212,7 +7212,7 @@
       <c r="AL143" s="3"/>
       <c r="AM143" s="3"/>
     </row>
-    <row r="144" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -7253,7 +7253,7 @@
       <c r="AL144" s="3"/>
       <c r="AM144" s="3"/>
     </row>
-    <row r="145" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -7294,7 +7294,7 @@
       <c r="AL145" s="3"/>
       <c r="AM145" s="3"/>
     </row>
-    <row r="146" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -7335,7 +7335,7 @@
       <c r="AL146" s="3"/>
       <c r="AM146" s="3"/>
     </row>
-    <row r="147" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -7376,7 +7376,7 @@
       <c r="AL147" s="3"/>
       <c r="AM147" s="3"/>
     </row>
-    <row r="148" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -7417,7 +7417,7 @@
       <c r="AL148" s="3"/>
       <c r="AM148" s="3"/>
     </row>
-    <row r="149" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -7458,7 +7458,7 @@
       <c r="AL149" s="3"/>
       <c r="AM149" s="3"/>
     </row>
-    <row r="150" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -7499,7 +7499,7 @@
       <c r="AL150" s="3"/>
       <c r="AM150" s="3"/>
     </row>
-    <row r="151" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -7540,7 +7540,7 @@
       <c r="AL151" s="3"/>
       <c r="AM151" s="3"/>
     </row>
-    <row r="152" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -7581,7 +7581,7 @@
       <c r="AL152" s="3"/>
       <c r="AM152" s="3"/>
     </row>
-    <row r="153" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -7622,7 +7622,7 @@
       <c r="AL153" s="3"/>
       <c r="AM153" s="3"/>
     </row>
-    <row r="154" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -7663,7 +7663,7 @@
       <c r="AL154" s="3"/>
       <c r="AM154" s="3"/>
     </row>
-    <row r="155" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -7704,7 +7704,7 @@
       <c r="AL155" s="3"/>
       <c r="AM155" s="3"/>
     </row>
-    <row r="156" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -7745,7 +7745,7 @@
       <c r="AL156" s="3"/>
       <c r="AM156" s="3"/>
     </row>
-    <row r="157" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -7786,7 +7786,7 @@
       <c r="AL157" s="3"/>
       <c r="AM157" s="3"/>
     </row>
-    <row r="158" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -7827,7 +7827,7 @@
       <c r="AL158" s="3"/>
       <c r="AM158" s="3"/>
     </row>
-    <row r="159" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -7868,7 +7868,7 @@
       <c r="AL159" s="3"/>
       <c r="AM159" s="3"/>
     </row>
-    <row r="160" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -7909,7 +7909,7 @@
       <c r="AL160" s="3"/>
       <c r="AM160" s="3"/>
     </row>
-    <row r="161" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -7950,7 +7950,7 @@
       <c r="AL161" s="3"/>
       <c r="AM161" s="3"/>
     </row>
-    <row r="162" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -7991,7 +7991,7 @@
       <c r="AL162" s="3"/>
       <c r="AM162" s="3"/>
     </row>
-    <row r="163" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -8032,7 +8032,7 @@
       <c r="AL163" s="3"/>
       <c r="AM163" s="3"/>
     </row>
-    <row r="164" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -8073,7 +8073,7 @@
       <c r="AL164" s="3"/>
       <c r="AM164" s="3"/>
     </row>
-    <row r="165" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -8114,7 +8114,7 @@
       <c r="AL165" s="3"/>
       <c r="AM165" s="3"/>
     </row>
-    <row r="166" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -8155,7 +8155,7 @@
       <c r="AL166" s="3"/>
       <c r="AM166" s="3"/>
     </row>
-    <row r="167" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -8196,7 +8196,7 @@
       <c r="AL167" s="3"/>
       <c r="AM167" s="3"/>
     </row>
-    <row r="168" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -8237,7 +8237,7 @@
       <c r="AL168" s="3"/>
       <c r="AM168" s="3"/>
     </row>
-    <row r="169" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -8278,7 +8278,7 @@
       <c r="AL169" s="3"/>
       <c r="AM169" s="3"/>
     </row>
-    <row r="170" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -8319,7 +8319,7 @@
       <c r="AL170" s="3"/>
       <c r="AM170" s="3"/>
     </row>
-    <row r="171" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -8360,7 +8360,7 @@
       <c r="AL171" s="3"/>
       <c r="AM171" s="3"/>
     </row>
-    <row r="172" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -8401,7 +8401,7 @@
       <c r="AL172" s="3"/>
       <c r="AM172" s="3"/>
     </row>
-    <row r="173" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -8442,7 +8442,7 @@
       <c r="AL173" s="3"/>
       <c r="AM173" s="3"/>
     </row>
-    <row r="174" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -8483,7 +8483,7 @@
       <c r="AL174" s="3"/>
       <c r="AM174" s="3"/>
     </row>
-    <row r="175" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -8524,7 +8524,7 @@
       <c r="AL175" s="3"/>
       <c r="AM175" s="3"/>
     </row>
-    <row r="176" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -8565,7 +8565,7 @@
       <c r="AL176" s="3"/>
       <c r="AM176" s="3"/>
     </row>
-    <row r="177" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -8606,7 +8606,7 @@
       <c r="AL177" s="3"/>
       <c r="AM177" s="3"/>
     </row>
-    <row r="178" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -8647,7 +8647,7 @@
       <c r="AL178" s="3"/>
       <c r="AM178" s="3"/>
     </row>
-    <row r="179" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -8688,7 +8688,7 @@
       <c r="AL179" s="3"/>
       <c r="AM179" s="3"/>
     </row>
-    <row r="180" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -8729,7 +8729,7 @@
       <c r="AL180" s="3"/>
       <c r="AM180" s="3"/>
     </row>
-    <row r="181" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -8770,7 +8770,7 @@
       <c r="AL181" s="3"/>
       <c r="AM181" s="3"/>
     </row>
-    <row r="182" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -8811,7 +8811,7 @@
       <c r="AL182" s="3"/>
       <c r="AM182" s="3"/>
     </row>
-    <row r="183" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -8852,7 +8852,7 @@
       <c r="AL183" s="3"/>
       <c r="AM183" s="3"/>
     </row>
-    <row r="184" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -8893,7 +8893,7 @@
       <c r="AL184" s="3"/>
       <c r="AM184" s="3"/>
     </row>
-    <row r="185" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -8934,7 +8934,7 @@
       <c r="AL185" s="3"/>
       <c r="AM185" s="3"/>
     </row>
-    <row r="186" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -8975,7 +8975,7 @@
       <c r="AL186" s="3"/>
       <c r="AM186" s="3"/>
     </row>
-    <row r="187" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -9016,7 +9016,7 @@
       <c r="AL187" s="3"/>
       <c r="AM187" s="3"/>
     </row>
-    <row r="188" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -9057,7 +9057,7 @@
       <c r="AL188" s="3"/>
       <c r="AM188" s="3"/>
     </row>
-    <row r="189" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -9098,7 +9098,7 @@
       <c r="AL189" s="3"/>
       <c r="AM189" s="3"/>
     </row>
-    <row r="190" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -9139,7 +9139,7 @@
       <c r="AL190" s="3"/>
       <c r="AM190" s="3"/>
     </row>
-    <row r="191" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -9180,7 +9180,7 @@
       <c r="AL191" s="3"/>
       <c r="AM191" s="3"/>
     </row>
-    <row r="192" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -9221,7 +9221,7 @@
       <c r="AL192" s="3"/>
       <c r="AM192" s="3"/>
     </row>
-    <row r="193" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -9262,7 +9262,7 @@
       <c r="AL193" s="3"/>
       <c r="AM193" s="3"/>
     </row>
-    <row r="194" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -9303,7 +9303,7 @@
       <c r="AL194" s="3"/>
       <c r="AM194" s="3"/>
     </row>
-    <row r="195" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -9344,7 +9344,7 @@
       <c r="AL195" s="3"/>
       <c r="AM195" s="3"/>
     </row>
-    <row r="196" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -9385,7 +9385,7 @@
       <c r="AL196" s="3"/>
       <c r="AM196" s="3"/>
     </row>
-    <row r="197" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -9426,7 +9426,7 @@
       <c r="AL197" s="3"/>
       <c r="AM197" s="3"/>
     </row>
-    <row r="198" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -9467,7 +9467,7 @@
       <c r="AL198" s="3"/>
       <c r="AM198" s="3"/>
     </row>
-    <row r="199" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -9508,7 +9508,7 @@
       <c r="AL199" s="3"/>
       <c r="AM199" s="3"/>
     </row>
-    <row r="200" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -9549,7 +9549,7 @@
       <c r="AL200" s="3"/>
       <c r="AM200" s="3"/>
     </row>
-    <row r="201" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -9590,7 +9590,7 @@
       <c r="AL201" s="3"/>
       <c r="AM201" s="3"/>
     </row>
-    <row r="202" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -9631,7 +9631,7 @@
       <c r="AL202" s="3"/>
       <c r="AM202" s="3"/>
     </row>
-    <row r="203" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -9672,7 +9672,7 @@
       <c r="AL203" s="3"/>
       <c r="AM203" s="3"/>
     </row>
-    <row r="204" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -9713,7 +9713,7 @@
       <c r="AL204" s="3"/>
       <c r="AM204" s="3"/>
     </row>
-    <row r="205" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -9754,7 +9754,7 @@
       <c r="AL205" s="3"/>
       <c r="AM205" s="3"/>
     </row>
-    <row r="206" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -9795,7 +9795,7 @@
       <c r="AL206" s="3"/>
       <c r="AM206" s="3"/>
     </row>
-    <row r="207" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -9836,7 +9836,7 @@
       <c r="AL207" s="3"/>
       <c r="AM207" s="3"/>
     </row>
-    <row r="208" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -9877,7 +9877,7 @@
       <c r="AL208" s="3"/>
       <c r="AM208" s="3"/>
     </row>
-    <row r="209" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -9918,7 +9918,7 @@
       <c r="AL209" s="3"/>
       <c r="AM209" s="3"/>
     </row>
-    <row r="210" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -9959,7 +9959,7 @@
       <c r="AL210" s="3"/>
       <c r="AM210" s="3"/>
     </row>
-    <row r="211" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -10000,7 +10000,7 @@
       <c r="AL211" s="3"/>
       <c r="AM211" s="3"/>
     </row>
-    <row r="212" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -10041,7 +10041,7 @@
       <c r="AL212" s="3"/>
       <c r="AM212" s="3"/>
     </row>
-    <row r="213" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -10082,7 +10082,7 @@
       <c r="AL213" s="3"/>
       <c r="AM213" s="3"/>
     </row>
-    <row r="214" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -10123,7 +10123,7 @@
       <c r="AL214" s="3"/>
       <c r="AM214" s="3"/>
     </row>
-    <row r="215" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -10164,7 +10164,7 @@
       <c r="AL215" s="3"/>
       <c r="AM215" s="3"/>
     </row>
-    <row r="216" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -10205,7 +10205,7 @@
       <c r="AL216" s="3"/>
       <c r="AM216" s="3"/>
     </row>
-    <row r="217" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -10246,7 +10246,7 @@
       <c r="AL217" s="3"/>
       <c r="AM217" s="3"/>
     </row>
-    <row r="218" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -10287,7 +10287,7 @@
       <c r="AL218" s="3"/>
       <c r="AM218" s="3"/>
     </row>
-    <row r="219" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -10328,7 +10328,7 @@
       <c r="AL219" s="3"/>
       <c r="AM219" s="3"/>
     </row>
-    <row r="220" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -10369,7 +10369,7 @@
       <c r="AL220" s="3"/>
       <c r="AM220" s="3"/>
     </row>
-    <row r="221" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -10410,7 +10410,7 @@
       <c r="AL221" s="3"/>
       <c r="AM221" s="3"/>
     </row>
-    <row r="222" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -10451,7 +10451,7 @@
       <c r="AL222" s="3"/>
       <c r="AM222" s="3"/>
     </row>
-    <row r="223" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -10492,7 +10492,7 @@
       <c r="AL223" s="3"/>
       <c r="AM223" s="3"/>
     </row>
-    <row r="224" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -10533,7 +10533,7 @@
       <c r="AL224" s="3"/>
       <c r="AM224" s="3"/>
     </row>
-    <row r="225" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -10574,7 +10574,7 @@
       <c r="AL225" s="3"/>
       <c r="AM225" s="3"/>
     </row>
-    <row r="226" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -10615,7 +10615,7 @@
       <c r="AL226" s="3"/>
       <c r="AM226" s="3"/>
     </row>
-    <row r="227" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -10656,7 +10656,7 @@
       <c r="AL227" s="3"/>
       <c r="AM227" s="3"/>
     </row>
-    <row r="228" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -10697,7 +10697,7 @@
       <c r="AL228" s="3"/>
       <c r="AM228" s="3"/>
     </row>
-    <row r="229" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -10738,7 +10738,7 @@
       <c r="AL229" s="3"/>
       <c r="AM229" s="3"/>
     </row>
-    <row r="230" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -10779,7 +10779,7 @@
       <c r="AL230" s="3"/>
       <c r="AM230" s="3"/>
     </row>
-    <row r="231" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -10820,7 +10820,7 @@
       <c r="AL231" s="3"/>
       <c r="AM231" s="3"/>
     </row>
-    <row r="232" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -10861,7 +10861,7 @@
       <c r="AL232" s="3"/>
       <c r="AM232" s="3"/>
     </row>
-    <row r="233" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -10902,7 +10902,7 @@
       <c r="AL233" s="3"/>
       <c r="AM233" s="3"/>
     </row>
-    <row r="234" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -10943,7 +10943,7 @@
       <c r="AL234" s="3"/>
       <c r="AM234" s="3"/>
     </row>
-    <row r="235" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -10984,7 +10984,7 @@
       <c r="AL235" s="3"/>
       <c r="AM235" s="3"/>
     </row>
-    <row r="236" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -11025,7 +11025,7 @@
       <c r="AL236" s="3"/>
       <c r="AM236" s="3"/>
     </row>
-    <row r="237" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -11066,7 +11066,7 @@
       <c r="AL237" s="3"/>
       <c r="AM237" s="3"/>
     </row>
-    <row r="238" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -11107,7 +11107,7 @@
       <c r="AL238" s="3"/>
       <c r="AM238" s="3"/>
     </row>
-    <row r="239" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -11148,7 +11148,7 @@
       <c r="AL239" s="3"/>
       <c r="AM239" s="3"/>
     </row>
-    <row r="240" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -11189,7 +11189,7 @@
       <c r="AL240" s="3"/>
       <c r="AM240" s="3"/>
     </row>
-    <row r="241" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -11230,7 +11230,7 @@
       <c r="AL241" s="3"/>
       <c r="AM241" s="3"/>
     </row>
-    <row r="242" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -11271,7 +11271,7 @@
       <c r="AL242" s="3"/>
       <c r="AM242" s="3"/>
     </row>
-    <row r="243" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -11312,7 +11312,7 @@
       <c r="AL243" s="3"/>
       <c r="AM243" s="3"/>
     </row>
-    <row r="244" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -11353,7 +11353,7 @@
       <c r="AL244" s="3"/>
       <c r="AM244" s="3"/>
     </row>
-    <row r="245" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -11394,7 +11394,7 @@
       <c r="AL245" s="3"/>
       <c r="AM245" s="3"/>
     </row>
-    <row r="246" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -11435,7 +11435,7 @@
       <c r="AL246" s="3"/>
       <c r="AM246" s="3"/>
     </row>
-    <row r="247" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -11476,7 +11476,7 @@
       <c r="AL247" s="3"/>
       <c r="AM247" s="3"/>
     </row>
-    <row r="248" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -11517,7 +11517,7 @@
       <c r="AL248" s="3"/>
       <c r="AM248" s="3"/>
     </row>
-    <row r="249" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -11558,7 +11558,7 @@
       <c r="AL249" s="3"/>
       <c r="AM249" s="3"/>
     </row>
-    <row r="250" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -11599,7 +11599,7 @@
       <c r="AL250" s="3"/>
       <c r="AM250" s="3"/>
     </row>
-    <row r="251" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -11640,7 +11640,7 @@
       <c r="AL251" s="3"/>
       <c r="AM251" s="3"/>
     </row>
-    <row r="252" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -11681,7 +11681,7 @@
       <c r="AL252" s="3"/>
       <c r="AM252" s="3"/>
     </row>
-    <row r="253" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -11722,7 +11722,7 @@
       <c r="AL253" s="3"/>
       <c r="AM253" s="3"/>
     </row>
-    <row r="254" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -11763,7 +11763,7 @@
       <c r="AL254" s="3"/>
       <c r="AM254" s="3"/>
     </row>
-    <row r="255" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -11804,7 +11804,7 @@
       <c r="AL255" s="3"/>
       <c r="AM255" s="3"/>
     </row>
-    <row r="256" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -11845,7 +11845,7 @@
       <c r="AL256" s="3"/>
       <c r="AM256" s="3"/>
     </row>
-    <row r="257" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -11886,7 +11886,7 @@
       <c r="AL257" s="3"/>
       <c r="AM257" s="3"/>
     </row>
-    <row r="258" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -11927,7 +11927,7 @@
       <c r="AL258" s="3"/>
       <c r="AM258" s="3"/>
     </row>
-    <row r="259" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -11968,7 +11968,7 @@
       <c r="AL259" s="3"/>
       <c r="AM259" s="3"/>
     </row>
-    <row r="260" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -12009,7 +12009,7 @@
       <c r="AL260" s="3"/>
       <c r="AM260" s="3"/>
     </row>
-    <row r="261" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -12050,7 +12050,7 @@
       <c r="AL261" s="3"/>
       <c r="AM261" s="3"/>
     </row>
-    <row r="262" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -12091,7 +12091,7 @@
       <c r="AL262" s="3"/>
       <c r="AM262" s="3"/>
     </row>
-    <row r="263" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -12132,7 +12132,7 @@
       <c r="AL263" s="3"/>
       <c r="AM263" s="3"/>
     </row>
-    <row r="264" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -12173,7 +12173,7 @@
       <c r="AL264" s="3"/>
       <c r="AM264" s="3"/>
     </row>
-    <row r="265" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -12214,7 +12214,7 @@
       <c r="AL265" s="3"/>
       <c r="AM265" s="3"/>
     </row>
-    <row r="266" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -12255,7 +12255,7 @@
       <c r="AL266" s="3"/>
       <c r="AM266" s="3"/>
     </row>
-    <row r="267" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -12296,7 +12296,7 @@
       <c r="AL267" s="3"/>
       <c r="AM267" s="3"/>
     </row>
-    <row r="268" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -12337,7 +12337,7 @@
       <c r="AL268" s="3"/>
       <c r="AM268" s="3"/>
     </row>
-    <row r="269" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -12378,7 +12378,7 @@
       <c r="AL269" s="3"/>
       <c r="AM269" s="3"/>
     </row>
-    <row r="270" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -12419,7 +12419,7 @@
       <c r="AL270" s="3"/>
       <c r="AM270" s="3"/>
     </row>
-    <row r="271" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -12460,7 +12460,7 @@
       <c r="AL271" s="3"/>
       <c r="AM271" s="3"/>
     </row>
-    <row r="272" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -12501,7 +12501,7 @@
       <c r="AL272" s="3"/>
       <c r="AM272" s="3"/>
     </row>
-    <row r="273" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -12542,7 +12542,7 @@
       <c r="AL273" s="3"/>
       <c r="AM273" s="3"/>
     </row>
-    <row r="274" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -12583,7 +12583,7 @@
       <c r="AL274" s="3"/>
       <c r="AM274" s="3"/>
     </row>
-    <row r="275" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -12624,7 +12624,7 @@
       <c r="AL275" s="3"/>
       <c r="AM275" s="3"/>
     </row>
-    <row r="276" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -12665,7 +12665,7 @@
       <c r="AL276" s="3"/>
       <c r="AM276" s="3"/>
     </row>
-    <row r="277" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -12706,7 +12706,7 @@
       <c r="AL277" s="3"/>
       <c r="AM277" s="3"/>
     </row>
-    <row r="278" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -12747,7 +12747,7 @@
       <c r="AL278" s="3"/>
       <c r="AM278" s="3"/>
     </row>
-    <row r="279" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -12788,7 +12788,7 @@
       <c r="AL279" s="3"/>
       <c r="AM279" s="3"/>
     </row>
-    <row r="280" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -12829,7 +12829,7 @@
       <c r="AL280" s="3"/>
       <c r="AM280" s="3"/>
     </row>
-    <row r="281" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -12870,7 +12870,7 @@
       <c r="AL281" s="3"/>
       <c r="AM281" s="3"/>
     </row>
-    <row r="282" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -12911,7 +12911,7 @@
       <c r="AL282" s="3"/>
       <c r="AM282" s="3"/>
     </row>
-    <row r="283" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -12952,7 +12952,7 @@
       <c r="AL283" s="3"/>
       <c r="AM283" s="3"/>
     </row>
-    <row r="284" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -12993,7 +12993,7 @@
       <c r="AL284" s="3"/>
       <c r="AM284" s="3"/>
     </row>
-    <row r="285" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -13034,7 +13034,7 @@
       <c r="AL285" s="3"/>
       <c r="AM285" s="3"/>
     </row>
-    <row r="286" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -13075,7 +13075,7 @@
       <c r="AL286" s="3"/>
       <c r="AM286" s="3"/>
     </row>
-    <row r="287" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -13116,7 +13116,7 @@
       <c r="AL287" s="3"/>
       <c r="AM287" s="3"/>
     </row>
-    <row r="288" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -13157,7 +13157,7 @@
       <c r="AL288" s="3"/>
       <c r="AM288" s="3"/>
     </row>
-    <row r="289" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -13198,7 +13198,7 @@
       <c r="AL289" s="3"/>
       <c r="AM289" s="3"/>
     </row>
-    <row r="290" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -13239,7 +13239,7 @@
       <c r="AL290" s="3"/>
       <c r="AM290" s="3"/>
     </row>
-    <row r="291" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -13280,7 +13280,7 @@
       <c r="AL291" s="3"/>
       <c r="AM291" s="3"/>
     </row>
-    <row r="292" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -13321,7 +13321,7 @@
       <c r="AL292" s="3"/>
       <c r="AM292" s="3"/>
     </row>
-    <row r="293" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -13362,7 +13362,7 @@
       <c r="AL293" s="3"/>
       <c r="AM293" s="3"/>
     </row>
-    <row r="294" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -13403,7 +13403,7 @@
       <c r="AL294" s="3"/>
       <c r="AM294" s="3"/>
     </row>
-    <row r="295" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -13444,7 +13444,7 @@
       <c r="AL295" s="3"/>
       <c r="AM295" s="3"/>
     </row>
-    <row r="296" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -13485,7 +13485,7 @@
       <c r="AL296" s="3"/>
       <c r="AM296" s="3"/>
     </row>
-    <row r="297" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -13526,7 +13526,7 @@
       <c r="AL297" s="3"/>
       <c r="AM297" s="3"/>
     </row>
-    <row r="298" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -13567,7 +13567,7 @@
       <c r="AL298" s="3"/>
       <c r="AM298" s="3"/>
     </row>
-    <row r="299" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -13608,7 +13608,7 @@
       <c r="AL299" s="3"/>
       <c r="AM299" s="3"/>
     </row>
-    <row r="300" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -13649,7 +13649,7 @@
       <c r="AL300" s="3"/>
       <c r="AM300" s="3"/>
     </row>
-    <row r="301" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -13690,7 +13690,7 @@
       <c r="AL301" s="3"/>
       <c r="AM301" s="3"/>
     </row>
-    <row r="302" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -13731,7 +13731,7 @@
       <c r="AL302" s="3"/>
       <c r="AM302" s="3"/>
     </row>
-    <row r="303" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -13772,7 +13772,7 @@
       <c r="AL303" s="3"/>
       <c r="AM303" s="3"/>
     </row>
-    <row r="304" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -13813,7 +13813,7 @@
       <c r="AL304" s="3"/>
       <c r="AM304" s="3"/>
     </row>
-    <row r="305" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -13854,7 +13854,7 @@
       <c r="AL305" s="3"/>
       <c r="AM305" s="3"/>
     </row>
-    <row r="306" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -13895,7 +13895,7 @@
       <c r="AL306" s="3"/>
       <c r="AM306" s="3"/>
     </row>
-    <row r="307" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -13936,7 +13936,7 @@
       <c r="AL307" s="3"/>
       <c r="AM307" s="3"/>
     </row>
-    <row r="308" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -13977,7 +13977,7 @@
       <c r="AL308" s="3"/>
       <c r="AM308" s="3"/>
     </row>
-    <row r="309" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -14018,7 +14018,7 @@
       <c r="AL309" s="3"/>
       <c r="AM309" s="3"/>
     </row>
-    <row r="310" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -14059,7 +14059,7 @@
       <c r="AL310" s="3"/>
       <c r="AM310" s="3"/>
     </row>
-    <row r="311" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -14100,7 +14100,7 @@
       <c r="AL311" s="3"/>
       <c r="AM311" s="3"/>
     </row>
-    <row r="312" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -14141,7 +14141,7 @@
       <c r="AL312" s="3"/>
       <c r="AM312" s="3"/>
     </row>
-    <row r="313" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -14182,7 +14182,7 @@
       <c r="AL313" s="3"/>
       <c r="AM313" s="3"/>
     </row>
-    <row r="314" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -14223,7 +14223,7 @@
       <c r="AL314" s="3"/>
       <c r="AM314" s="3"/>
     </row>
-    <row r="315" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -14264,7 +14264,7 @@
       <c r="AL315" s="3"/>
       <c r="AM315" s="3"/>
     </row>
-    <row r="316" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -14305,7 +14305,7 @@
       <c r="AL316" s="3"/>
       <c r="AM316" s="3"/>
     </row>
-    <row r="317" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -14346,7 +14346,7 @@
       <c r="AL317" s="3"/>
       <c r="AM317" s="3"/>
     </row>
-    <row r="318" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -14387,7 +14387,7 @@
       <c r="AL318" s="3"/>
       <c r="AM318" s="3"/>
     </row>
-    <row r="319" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -14428,7 +14428,7 @@
       <c r="AL319" s="3"/>
       <c r="AM319" s="3"/>
     </row>
-    <row r="320" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -14469,7 +14469,7 @@
       <c r="AL320" s="3"/>
       <c r="AM320" s="3"/>
     </row>
-    <row r="321" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -14510,7 +14510,7 @@
       <c r="AL321" s="3"/>
       <c r="AM321" s="3"/>
     </row>
-    <row r="322" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -14551,7 +14551,7 @@
       <c r="AL322" s="3"/>
       <c r="AM322" s="3"/>
     </row>
-    <row r="323" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -14592,7 +14592,7 @@
       <c r="AL323" s="3"/>
       <c r="AM323" s="3"/>
     </row>
-    <row r="324" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -14633,7 +14633,7 @@
       <c r="AL324" s="3"/>
       <c r="AM324" s="3"/>
     </row>
-    <row r="325" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -14674,7 +14674,7 @@
       <c r="AL325" s="3"/>
       <c r="AM325" s="3"/>
     </row>
-    <row r="326" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -14715,7 +14715,7 @@
       <c r="AL326" s="3"/>
       <c r="AM326" s="3"/>
     </row>
-    <row r="327" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -14756,7 +14756,7 @@
       <c r="AL327" s="3"/>
       <c r="AM327" s="3"/>
     </row>
-    <row r="328" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -14797,7 +14797,7 @@
       <c r="AL328" s="3"/>
       <c r="AM328" s="3"/>
     </row>
-    <row r="329" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -14838,7 +14838,7 @@
       <c r="AL329" s="3"/>
       <c r="AM329" s="3"/>
     </row>
-    <row r="330" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -14879,7 +14879,7 @@
       <c r="AL330" s="3"/>
       <c r="AM330" s="3"/>
     </row>
-    <row r="331" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -14920,7 +14920,7 @@
       <c r="AL331" s="3"/>
       <c r="AM331" s="3"/>
     </row>
-    <row r="332" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -14961,7 +14961,7 @@
       <c r="AL332" s="3"/>
       <c r="AM332" s="3"/>
     </row>
-    <row r="333" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -15002,7 +15002,7 @@
       <c r="AL333" s="3"/>
       <c r="AM333" s="3"/>
     </row>
-    <row r="334" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -15043,7 +15043,7 @@
       <c r="AL334" s="3"/>
       <c r="AM334" s="3"/>
     </row>
-    <row r="335" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -15084,7 +15084,7 @@
       <c r="AL335" s="3"/>
       <c r="AM335" s="3"/>
     </row>
-    <row r="336" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -15125,7 +15125,7 @@
       <c r="AL336" s="3"/>
       <c r="AM336" s="3"/>
     </row>
-    <row r="337" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -15166,7 +15166,7 @@
       <c r="AL337" s="3"/>
       <c r="AM337" s="3"/>
     </row>
-    <row r="338" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -15207,7 +15207,7 @@
       <c r="AL338" s="3"/>
       <c r="AM338" s="3"/>
     </row>
-    <row r="339" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -15248,7 +15248,7 @@
       <c r="AL339" s="3"/>
       <c r="AM339" s="3"/>
     </row>
-    <row r="340" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -15289,7 +15289,7 @@
       <c r="AL340" s="3"/>
       <c r="AM340" s="3"/>
     </row>
-    <row r="341" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -15330,7 +15330,7 @@
       <c r="AL341" s="3"/>
       <c r="AM341" s="3"/>
     </row>
-    <row r="342" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -15371,7 +15371,7 @@
       <c r="AL342" s="3"/>
       <c r="AM342" s="3"/>
     </row>
-    <row r="343" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -15412,7 +15412,7 @@
       <c r="AL343" s="3"/>
       <c r="AM343" s="3"/>
     </row>
-    <row r="344" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -15453,7 +15453,7 @@
       <c r="AL344" s="3"/>
       <c r="AM344" s="3"/>
     </row>
-    <row r="345" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -15494,7 +15494,7 @@
       <c r="AL345" s="3"/>
       <c r="AM345" s="3"/>
     </row>
-    <row r="346" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -15535,7 +15535,7 @@
       <c r="AL346" s="3"/>
       <c r="AM346" s="3"/>
     </row>
-    <row r="347" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -15576,7 +15576,7 @@
       <c r="AL347" s="3"/>
       <c r="AM347" s="3"/>
     </row>
-    <row r="348" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -15617,7 +15617,7 @@
       <c r="AL348" s="3"/>
       <c r="AM348" s="3"/>
     </row>
-    <row r="349" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -15658,7 +15658,7 @@
       <c r="AL349" s="3"/>
       <c r="AM349" s="3"/>
     </row>
-    <row r="350" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -15699,7 +15699,7 @@
       <c r="AL350" s="3"/>
       <c r="AM350" s="3"/>
     </row>
-    <row r="351" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -15740,7 +15740,7 @@
       <c r="AL351" s="3"/>
       <c r="AM351" s="3"/>
     </row>
-    <row r="352" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -15781,7 +15781,7 @@
       <c r="AL352" s="3"/>
       <c r="AM352" s="3"/>
     </row>
-    <row r="353" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -15822,7 +15822,7 @@
       <c r="AL353" s="3"/>
       <c r="AM353" s="3"/>
     </row>
-    <row r="354" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -15863,7 +15863,7 @@
       <c r="AL354" s="3"/>
       <c r="AM354" s="3"/>
     </row>
-    <row r="355" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -15904,7 +15904,7 @@
       <c r="AL355" s="3"/>
       <c r="AM355" s="3"/>
     </row>
-    <row r="356" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -15945,7 +15945,7 @@
       <c r="AL356" s="3"/>
       <c r="AM356" s="3"/>
     </row>
-    <row r="357" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -15986,7 +15986,7 @@
       <c r="AL357" s="3"/>
       <c r="AM357" s="3"/>
     </row>
-    <row r="358" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -16027,7 +16027,7 @@
       <c r="AL358" s="3"/>
       <c r="AM358" s="3"/>
     </row>
-    <row r="359" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -16068,7 +16068,7 @@
       <c r="AL359" s="3"/>
       <c r="AM359" s="3"/>
     </row>
-    <row r="360" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -16109,7 +16109,7 @@
       <c r="AL360" s="3"/>
       <c r="AM360" s="3"/>
     </row>
-    <row r="361" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -16150,7 +16150,7 @@
       <c r="AL361" s="3"/>
       <c r="AM361" s="3"/>
     </row>
-    <row r="362" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -16191,7 +16191,7 @@
       <c r="AL362" s="3"/>
       <c r="AM362" s="3"/>
     </row>
-    <row r="363" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -16232,7 +16232,7 @@
       <c r="AL363" s="3"/>
       <c r="AM363" s="3"/>
     </row>
-    <row r="364" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -16273,7 +16273,7 @@
       <c r="AL364" s="3"/>
       <c r="AM364" s="3"/>
     </row>
-    <row r="365" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -16314,7 +16314,7 @@
       <c r="AL365" s="3"/>
       <c r="AM365" s="3"/>
     </row>
-    <row r="366" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -16355,7 +16355,7 @@
       <c r="AL366" s="3"/>
       <c r="AM366" s="3"/>
     </row>
-    <row r="367" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -16396,7 +16396,7 @@
       <c r="AL367" s="3"/>
       <c r="AM367" s="3"/>
     </row>
-    <row r="368" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -16437,7 +16437,7 @@
       <c r="AL368" s="3"/>
       <c r="AM368" s="3"/>
     </row>
-    <row r="369" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -16478,7 +16478,7 @@
       <c r="AL369" s="3"/>
       <c r="AM369" s="3"/>
     </row>
-    <row r="370" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -16519,7 +16519,7 @@
       <c r="AL370" s="3"/>
       <c r="AM370" s="3"/>
     </row>
-    <row r="371" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -16560,7 +16560,7 @@
       <c r="AL371" s="3"/>
       <c r="AM371" s="3"/>
     </row>
-    <row r="372" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -16601,7 +16601,7 @@
       <c r="AL372" s="3"/>
       <c r="AM372" s="3"/>
     </row>
-    <row r="373" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -16642,7 +16642,7 @@
       <c r="AL373" s="3"/>
       <c r="AM373" s="3"/>
     </row>
-    <row r="374" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -16683,7 +16683,7 @@
       <c r="AL374" s="3"/>
       <c r="AM374" s="3"/>
     </row>
-    <row r="375" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -16724,7 +16724,7 @@
       <c r="AL375" s="3"/>
       <c r="AM375" s="3"/>
     </row>
-    <row r="376" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -16765,7 +16765,7 @@
       <c r="AL376" s="3"/>
       <c r="AM376" s="3"/>
     </row>
-    <row r="377" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -16806,7 +16806,7 @@
       <c r="AL377" s="3"/>
       <c r="AM377" s="3"/>
     </row>
-    <row r="378" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -16847,7 +16847,7 @@
       <c r="AL378" s="3"/>
       <c r="AM378" s="3"/>
     </row>
-    <row r="379" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -16888,7 +16888,7 @@
       <c r="AL379" s="3"/>
       <c r="AM379" s="3"/>
     </row>
-    <row r="380" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -16929,7 +16929,7 @@
       <c r="AL380" s="3"/>
       <c r="AM380" s="3"/>
     </row>
-    <row r="381" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -16970,7 +16970,7 @@
       <c r="AL381" s="3"/>
       <c r="AM381" s="3"/>
     </row>
-    <row r="382" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -17011,7 +17011,7 @@
       <c r="AL382" s="3"/>
       <c r="AM382" s="3"/>
     </row>
-    <row r="383" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -17052,7 +17052,7 @@
       <c r="AL383" s="3"/>
       <c r="AM383" s="3"/>
     </row>
-    <row r="384" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -17093,7 +17093,7 @@
       <c r="AL384" s="3"/>
       <c r="AM384" s="3"/>
     </row>
-    <row r="385" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -17134,7 +17134,7 @@
       <c r="AL385" s="3"/>
       <c r="AM385" s="3"/>
     </row>
-    <row r="386" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -17175,7 +17175,7 @@
       <c r="AL386" s="3"/>
       <c r="AM386" s="3"/>
     </row>
-    <row r="387" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -17216,7 +17216,7 @@
       <c r="AL387" s="3"/>
       <c r="AM387" s="3"/>
     </row>
-    <row r="388" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -17257,7 +17257,7 @@
       <c r="AL388" s="3"/>
       <c r="AM388" s="3"/>
     </row>
-    <row r="389" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -17298,7 +17298,7 @@
       <c r="AL389" s="3"/>
       <c r="AM389" s="3"/>
     </row>
-    <row r="390" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -17339,7 +17339,7 @@
       <c r="AL390" s="3"/>
       <c r="AM390" s="3"/>
     </row>
-    <row r="391" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -17380,7 +17380,7 @@
       <c r="AL391" s="3"/>
       <c r="AM391" s="3"/>
     </row>
-    <row r="392" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -17421,7 +17421,7 @@
       <c r="AL392" s="3"/>
       <c r="AM392" s="3"/>
     </row>
-    <row r="393" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -17462,7 +17462,7 @@
       <c r="AL393" s="3"/>
       <c r="AM393" s="3"/>
     </row>
-    <row r="394" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -17503,7 +17503,7 @@
       <c r="AL394" s="3"/>
       <c r="AM394" s="3"/>
     </row>
-    <row r="395" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -17544,7 +17544,7 @@
       <c r="AL395" s="3"/>
       <c r="AM395" s="3"/>
     </row>
-    <row r="396" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -17585,7 +17585,7 @@
       <c r="AL396" s="3"/>
       <c r="AM396" s="3"/>
     </row>
-    <row r="397" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -17626,7 +17626,7 @@
       <c r="AL397" s="3"/>
       <c r="AM397" s="3"/>
     </row>
-    <row r="398" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -17667,7 +17667,7 @@
       <c r="AL398" s="3"/>
       <c r="AM398" s="3"/>
     </row>
-    <row r="399" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -17708,7 +17708,7 @@
       <c r="AL399" s="3"/>
       <c r="AM399" s="3"/>
     </row>
-    <row r="400" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -17749,7 +17749,7 @@
       <c r="AL400" s="3"/>
       <c r="AM400" s="3"/>
     </row>
-    <row r="401" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -17790,7 +17790,7 @@
       <c r="AL401" s="3"/>
       <c r="AM401" s="3"/>
     </row>
-    <row r="402" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -17831,7 +17831,7 @@
       <c r="AL402" s="3"/>
       <c r="AM402" s="3"/>
     </row>
-    <row r="403" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -17872,7 +17872,7 @@
       <c r="AL403" s="3"/>
       <c r="AM403" s="3"/>
     </row>
-    <row r="404" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -17913,7 +17913,7 @@
       <c r="AL404" s="3"/>
       <c r="AM404" s="3"/>
     </row>
-    <row r="405" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -17954,7 +17954,7 @@
       <c r="AL405" s="3"/>
       <c r="AM405" s="3"/>
     </row>
-    <row r="406" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -17995,7 +17995,7 @@
       <c r="AL406" s="3"/>
       <c r="AM406" s="3"/>
     </row>
-    <row r="407" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -18036,7 +18036,7 @@
       <c r="AL407" s="3"/>
       <c r="AM407" s="3"/>
     </row>
-    <row r="408" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -18077,7 +18077,7 @@
       <c r="AL408" s="3"/>
       <c r="AM408" s="3"/>
     </row>
-    <row r="409" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -18118,7 +18118,7 @@
       <c r="AL409" s="3"/>
       <c r="AM409" s="3"/>
     </row>
-    <row r="410" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -18159,7 +18159,7 @@
       <c r="AL410" s="3"/>
       <c r="AM410" s="3"/>
     </row>
-    <row r="411" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -18200,7 +18200,7 @@
       <c r="AL411" s="3"/>
       <c r="AM411" s="3"/>
     </row>
-    <row r="412" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -18241,7 +18241,7 @@
       <c r="AL412" s="3"/>
       <c r="AM412" s="3"/>
     </row>
-    <row r="413" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -18282,7 +18282,7 @@
       <c r="AL413" s="3"/>
       <c r="AM413" s="3"/>
     </row>
-    <row r="414" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -18323,7 +18323,7 @@
       <c r="AL414" s="3"/>
       <c r="AM414" s="3"/>
     </row>
-    <row r="415" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -18364,7 +18364,7 @@
       <c r="AL415" s="3"/>
       <c r="AM415" s="3"/>
     </row>
-    <row r="416" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -18405,7 +18405,7 @@
       <c r="AL416" s="3"/>
       <c r="AM416" s="3"/>
     </row>
-    <row r="417" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -18446,7 +18446,7 @@
       <c r="AL417" s="3"/>
       <c r="AM417" s="3"/>
     </row>
-    <row r="418" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -18487,7 +18487,7 @@
       <c r="AL418" s="3"/>
       <c r="AM418" s="3"/>
     </row>
-    <row r="419" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -18528,7 +18528,7 @@
       <c r="AL419" s="3"/>
       <c r="AM419" s="3"/>
     </row>
-    <row r="420" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -18569,7 +18569,7 @@
       <c r="AL420" s="3"/>
       <c r="AM420" s="3"/>
     </row>
-    <row r="421" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -18610,7 +18610,7 @@
       <c r="AL421" s="3"/>
       <c r="AM421" s="3"/>
     </row>
-    <row r="422" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -18651,7 +18651,7 @@
       <c r="AL422" s="3"/>
       <c r="AM422" s="3"/>
     </row>
-    <row r="423" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -18692,7 +18692,7 @@
       <c r="AL423" s="3"/>
       <c r="AM423" s="3"/>
     </row>
-    <row r="424" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -18733,7 +18733,7 @@
       <c r="AL424" s="3"/>
       <c r="AM424" s="3"/>
     </row>
-    <row r="425" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -18774,7 +18774,7 @@
       <c r="AL425" s="3"/>
       <c r="AM425" s="3"/>
     </row>
-    <row r="426" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -18815,7 +18815,7 @@
       <c r="AL426" s="3"/>
       <c r="AM426" s="3"/>
     </row>
-    <row r="427" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -18856,7 +18856,7 @@
       <c r="AL427" s="3"/>
       <c r="AM427" s="3"/>
     </row>
-    <row r="428" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -18897,7 +18897,7 @@
       <c r="AL428" s="3"/>
       <c r="AM428" s="3"/>
     </row>
-    <row r="429" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -18938,7 +18938,7 @@
       <c r="AL429" s="3"/>
       <c r="AM429" s="3"/>
     </row>
-    <row r="430" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -18979,7 +18979,7 @@
       <c r="AL430" s="3"/>
       <c r="AM430" s="3"/>
     </row>
-    <row r="431" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -19020,7 +19020,7 @@
       <c r="AL431" s="3"/>
       <c r="AM431" s="3"/>
     </row>
-    <row r="432" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -19061,7 +19061,7 @@
       <c r="AL432" s="3"/>
       <c r="AM432" s="3"/>
     </row>
-    <row r="433" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -19102,7 +19102,7 @@
       <c r="AL433" s="3"/>
       <c r="AM433" s="3"/>
     </row>
-    <row r="434" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -19143,7 +19143,7 @@
       <c r="AL434" s="3"/>
       <c r="AM434" s="3"/>
     </row>
-    <row r="435" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -19184,7 +19184,7 @@
       <c r="AL435" s="3"/>
       <c r="AM435" s="3"/>
     </row>
-    <row r="436" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -19225,7 +19225,7 @@
       <c r="AL436" s="3"/>
       <c r="AM436" s="3"/>
     </row>
-    <row r="437" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -19266,7 +19266,7 @@
       <c r="AL437" s="3"/>
       <c r="AM437" s="3"/>
     </row>
-    <row r="438" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -19307,7 +19307,7 @@
       <c r="AL438" s="3"/>
       <c r="AM438" s="3"/>
     </row>
-    <row r="439" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -19348,7 +19348,7 @@
       <c r="AL439" s="3"/>
       <c r="AM439" s="3"/>
     </row>
-    <row r="440" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -19389,7 +19389,7 @@
       <c r="AL440" s="3"/>
       <c r="AM440" s="3"/>
     </row>
-    <row r="441" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -19430,7 +19430,7 @@
       <c r="AL441" s="3"/>
       <c r="AM441" s="3"/>
     </row>
-    <row r="442" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -19471,7 +19471,7 @@
       <c r="AL442" s="3"/>
       <c r="AM442" s="3"/>
     </row>
-    <row r="443" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -19512,7 +19512,7 @@
       <c r="AL443" s="3"/>
       <c r="AM443" s="3"/>
     </row>
-    <row r="444" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -19553,7 +19553,7 @@
       <c r="AL444" s="3"/>
       <c r="AM444" s="3"/>
     </row>
-    <row r="445" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -19594,7 +19594,7 @@
       <c r="AL445" s="3"/>
       <c r="AM445" s="3"/>
     </row>
-    <row r="446" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -19635,7 +19635,7 @@
       <c r="AL446" s="3"/>
       <c r="AM446" s="3"/>
     </row>
-    <row r="447" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -19676,7 +19676,7 @@
       <c r="AL447" s="3"/>
       <c r="AM447" s="3"/>
     </row>
-    <row r="448" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -19717,7 +19717,7 @@
       <c r="AL448" s="3"/>
       <c r="AM448" s="3"/>
     </row>
-    <row r="449" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -19758,7 +19758,7 @@
       <c r="AL449" s="3"/>
       <c r="AM449" s="3"/>
     </row>
-    <row r="450" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -19799,7 +19799,7 @@
       <c r="AL450" s="3"/>
       <c r="AM450" s="3"/>
     </row>
-    <row r="451" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -19840,7 +19840,7 @@
       <c r="AL451" s="3"/>
       <c r="AM451" s="3"/>
     </row>
-    <row r="452" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -19881,7 +19881,7 @@
       <c r="AL452" s="3"/>
       <c r="AM452" s="3"/>
     </row>
-    <row r="453" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -19922,7 +19922,7 @@
       <c r="AL453" s="3"/>
       <c r="AM453" s="3"/>
     </row>
-    <row r="454" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -19963,7 +19963,7 @@
       <c r="AL454" s="3"/>
       <c r="AM454" s="3"/>
     </row>
-    <row r="455" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -20004,7 +20004,7 @@
       <c r="AL455" s="3"/>
       <c r="AM455" s="3"/>
     </row>
-    <row r="456" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -20045,7 +20045,7 @@
       <c r="AL456" s="3"/>
       <c r="AM456" s="3"/>
     </row>
-    <row r="457" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -20086,7 +20086,7 @@
       <c r="AL457" s="3"/>
       <c r="AM457" s="3"/>
     </row>
-    <row r="458" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -20127,7 +20127,7 @@
       <c r="AL458" s="3"/>
       <c r="AM458" s="3"/>
     </row>
-    <row r="459" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -20168,7 +20168,7 @@
       <c r="AL459" s="3"/>
       <c r="AM459" s="3"/>
     </row>
-    <row r="460" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -20209,7 +20209,7 @@
       <c r="AL460" s="3"/>
       <c r="AM460" s="3"/>
     </row>
-    <row r="461" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -20250,7 +20250,7 @@
       <c r="AL461" s="3"/>
       <c r="AM461" s="3"/>
     </row>
-    <row r="462" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -20291,7 +20291,7 @@
       <c r="AL462" s="3"/>
       <c r="AM462" s="3"/>
     </row>
-    <row r="463" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -20332,7 +20332,7 @@
       <c r="AL463" s="3"/>
       <c r="AM463" s="3"/>
     </row>
-    <row r="464" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -20373,7 +20373,7 @@
       <c r="AL464" s="3"/>
       <c r="AM464" s="3"/>
     </row>
-    <row r="465" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -20414,7 +20414,7 @@
       <c r="AL465" s="3"/>
       <c r="AM465" s="3"/>
     </row>
-    <row r="466" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -20455,7 +20455,7 @@
       <c r="AL466" s="3"/>
       <c r="AM466" s="3"/>
     </row>
-    <row r="467" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -20496,7 +20496,7 @@
       <c r="AL467" s="3"/>
       <c r="AM467" s="3"/>
     </row>
-    <row r="468" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -20537,7 +20537,7 @@
       <c r="AL468" s="3"/>
       <c r="AM468" s="3"/>
     </row>
-    <row r="469" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -20578,7 +20578,7 @@
       <c r="AL469" s="3"/>
       <c r="AM469" s="3"/>
     </row>
-    <row r="470" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -20619,7 +20619,7 @@
       <c r="AL470" s="3"/>
       <c r="AM470" s="3"/>
     </row>
-    <row r="471" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -20660,7 +20660,7 @@
       <c r="AL471" s="3"/>
       <c r="AM471" s="3"/>
     </row>
-    <row r="472" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -20701,7 +20701,7 @@
       <c r="AL472" s="3"/>
       <c r="AM472" s="3"/>
     </row>
-    <row r="473" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -20742,7 +20742,7 @@
       <c r="AL473" s="3"/>
       <c r="AM473" s="3"/>
     </row>
-    <row r="474" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -20783,7 +20783,7 @@
       <c r="AL474" s="3"/>
       <c r="AM474" s="3"/>
     </row>
-    <row r="475" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -20824,7 +20824,7 @@
       <c r="AL475" s="3"/>
       <c r="AM475" s="3"/>
     </row>
-    <row r="476" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -20865,7 +20865,7 @@
       <c r="AL476" s="3"/>
       <c r="AM476" s="3"/>
     </row>
-    <row r="477" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -20906,7 +20906,7 @@
       <c r="AL477" s="3"/>
       <c r="AM477" s="3"/>
     </row>
-    <row r="478" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -20947,7 +20947,7 @@
       <c r="AL478" s="3"/>
       <c r="AM478" s="3"/>
     </row>
-    <row r="479" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -20988,7 +20988,7 @@
       <c r="AL479" s="3"/>
       <c r="AM479" s="3"/>
     </row>
-    <row r="480" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -21029,7 +21029,7 @@
       <c r="AL480" s="3"/>
       <c r="AM480" s="3"/>
     </row>
-    <row r="481" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -21070,7 +21070,7 @@
       <c r="AL481" s="3"/>
       <c r="AM481" s="3"/>
     </row>
-    <row r="482" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -21111,7 +21111,7 @@
       <c r="AL482" s="3"/>
       <c r="AM482" s="3"/>
     </row>
-    <row r="483" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -21152,7 +21152,7 @@
       <c r="AL483" s="3"/>
       <c r="AM483" s="3"/>
     </row>
-    <row r="484" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -21193,7 +21193,7 @@
       <c r="AL484" s="3"/>
       <c r="AM484" s="3"/>
     </row>
-    <row r="485" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -21234,7 +21234,7 @@
       <c r="AL485" s="3"/>
       <c r="AM485" s="3"/>
     </row>
-    <row r="486" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -21275,7 +21275,7 @@
       <c r="AL486" s="3"/>
       <c r="AM486" s="3"/>
     </row>
-    <row r="487" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -21316,7 +21316,7 @@
       <c r="AL487" s="3"/>
       <c r="AM487" s="3"/>
     </row>
-    <row r="488" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -21357,7 +21357,7 @@
       <c r="AL488" s="3"/>
       <c r="AM488" s="3"/>
     </row>
-    <row r="489" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -21398,7 +21398,7 @@
       <c r="AL489" s="3"/>
       <c r="AM489" s="3"/>
     </row>
-    <row r="490" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -21439,7 +21439,7 @@
       <c r="AL490" s="3"/>
       <c r="AM490" s="3"/>
     </row>
-    <row r="491" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -21480,7 +21480,7 @@
       <c r="AL491" s="3"/>
       <c r="AM491" s="3"/>
     </row>
-    <row r="492" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -21521,7 +21521,7 @@
       <c r="AL492" s="3"/>
       <c r="AM492" s="3"/>
     </row>
-    <row r="493" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -21562,7 +21562,7 @@
       <c r="AL493" s="3"/>
       <c r="AM493" s="3"/>
     </row>
-    <row r="494" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -21603,7 +21603,7 @@
       <c r="AL494" s="3"/>
       <c r="AM494" s="3"/>
     </row>
-    <row r="495" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -21644,7 +21644,7 @@
       <c r="AL495" s="3"/>
       <c r="AM495" s="3"/>
     </row>
-    <row r="496" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -21685,7 +21685,7 @@
       <c r="AL496" s="3"/>
       <c r="AM496" s="3"/>
     </row>
-    <row r="497" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -21726,7 +21726,7 @@
       <c r="AL497" s="3"/>
       <c r="AM497" s="3"/>
     </row>
-    <row r="498" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -21767,7 +21767,7 @@
       <c r="AL498" s="3"/>
       <c r="AM498" s="3"/>
     </row>
-    <row r="499" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -21808,7 +21808,7 @@
       <c r="AL499" s="3"/>
       <c r="AM499" s="3"/>
     </row>
-    <row r="500" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -21849,7 +21849,7 @@
       <c r="AL500" s="3"/>
       <c r="AM500" s="3"/>
     </row>
-    <row r="501" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -21890,7 +21890,7 @@
       <c r="AL501" s="3"/>
       <c r="AM501" s="3"/>
     </row>
-    <row r="502" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -21931,7 +21931,7 @@
       <c r="AL502" s="3"/>
       <c r="AM502" s="3"/>
     </row>
-    <row r="503" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -21972,7 +21972,7 @@
       <c r="AL503" s="3"/>
       <c r="AM503" s="3"/>
     </row>
-    <row r="504" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -22013,7 +22013,7 @@
       <c r="AL504" s="3"/>
       <c r="AM504" s="3"/>
     </row>
-    <row r="505" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -22054,7 +22054,7 @@
       <c r="AL505" s="3"/>
       <c r="AM505" s="3"/>
     </row>
-    <row r="506" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -22095,7 +22095,7 @@
       <c r="AL506" s="3"/>
       <c r="AM506" s="3"/>
     </row>
-    <row r="507" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -22136,7 +22136,7 @@
       <c r="AL507" s="3"/>
       <c r="AM507" s="3"/>
     </row>
-    <row r="508" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -22177,7 +22177,7 @@
       <c r="AL508" s="3"/>
       <c r="AM508" s="3"/>
     </row>
-    <row r="509" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -22218,7 +22218,7 @@
       <c r="AL509" s="3"/>
       <c r="AM509" s="3"/>
     </row>
-    <row r="510" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -22259,7 +22259,7 @@
       <c r="AL510" s="3"/>
       <c r="AM510" s="3"/>
     </row>
-    <row r="511" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -22300,7 +22300,7 @@
       <c r="AL511" s="3"/>
       <c r="AM511" s="3"/>
     </row>
-    <row r="512" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -22341,7 +22341,7 @@
       <c r="AL512" s="3"/>
       <c r="AM512" s="3"/>
     </row>
-    <row r="513" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -22382,7 +22382,7 @@
       <c r="AL513" s="3"/>
       <c r="AM513" s="3"/>
     </row>
-    <row r="514" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -22423,7 +22423,7 @@
       <c r="AL514" s="3"/>
       <c r="AM514" s="3"/>
     </row>
-    <row r="515" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -22464,7 +22464,7 @@
       <c r="AL515" s="3"/>
       <c r="AM515" s="3"/>
     </row>
-    <row r="516" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -22505,7 +22505,7 @@
       <c r="AL516" s="3"/>
       <c r="AM516" s="3"/>
     </row>
-    <row r="517" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -22546,7 +22546,7 @@
       <c r="AL517" s="3"/>
       <c r="AM517" s="3"/>
     </row>
-    <row r="518" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -22587,7 +22587,7 @@
       <c r="AL518" s="3"/>
       <c r="AM518" s="3"/>
     </row>
-    <row r="519" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -22628,7 +22628,7 @@
       <c r="AL519" s="3"/>
       <c r="AM519" s="3"/>
     </row>
-    <row r="520" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -22669,7 +22669,7 @@
       <c r="AL520" s="3"/>
       <c r="AM520" s="3"/>
     </row>
-    <row r="521" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -22710,7 +22710,7 @@
       <c r="AL521" s="3"/>
       <c r="AM521" s="3"/>
     </row>
-    <row r="522" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -22751,7 +22751,7 @@
       <c r="AL522" s="3"/>
       <c r="AM522" s="3"/>
     </row>
-    <row r="523" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -22792,7 +22792,7 @@
       <c r="AL523" s="3"/>
       <c r="AM523" s="3"/>
     </row>
-    <row r="524" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -22833,7 +22833,7 @@
       <c r="AL524" s="3"/>
       <c r="AM524" s="3"/>
     </row>
-    <row r="525" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -22874,7 +22874,7 @@
       <c r="AL525" s="3"/>
       <c r="AM525" s="3"/>
     </row>
-    <row r="526" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -22915,7 +22915,7 @@
       <c r="AL526" s="3"/>
       <c r="AM526" s="3"/>
     </row>
-    <row r="527" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -22956,7 +22956,7 @@
       <c r="AL527" s="3"/>
       <c r="AM527" s="3"/>
     </row>
-    <row r="528" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -22997,7 +22997,7 @@
       <c r="AL528" s="3"/>
       <c r="AM528" s="3"/>
     </row>
-    <row r="529" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -23038,7 +23038,7 @@
       <c r="AL529" s="3"/>
       <c r="AM529" s="3"/>
     </row>
-    <row r="530" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -23079,7 +23079,7 @@
       <c r="AL530" s="3"/>
       <c r="AM530" s="3"/>
     </row>
-    <row r="531" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -23120,7 +23120,7 @@
       <c r="AL531" s="3"/>
       <c r="AM531" s="3"/>
     </row>
-    <row r="532" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -23161,7 +23161,7 @@
       <c r="AL532" s="3"/>
       <c r="AM532" s="3"/>
     </row>
-    <row r="533" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -23202,7 +23202,7 @@
       <c r="AL533" s="3"/>
       <c r="AM533" s="3"/>
     </row>
-    <row r="534" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -23243,7 +23243,7 @@
       <c r="AL534" s="3"/>
       <c r="AM534" s="3"/>
     </row>
-    <row r="535" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -23284,7 +23284,7 @@
       <c r="AL535" s="3"/>
       <c r="AM535" s="3"/>
     </row>
-    <row r="536" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -23325,7 +23325,7 @@
       <c r="AL536" s="3"/>
       <c r="AM536" s="3"/>
     </row>
-    <row r="537" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -23366,7 +23366,7 @@
       <c r="AL537" s="3"/>
       <c r="AM537" s="3"/>
     </row>
-    <row r="538" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -23407,7 +23407,7 @@
       <c r="AL538" s="3"/>
       <c r="AM538" s="3"/>
     </row>
-    <row r="539" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -23448,7 +23448,7 @@
       <c r="AL539" s="3"/>
       <c r="AM539" s="3"/>
     </row>
-    <row r="540" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -23489,7 +23489,7 @@
       <c r="AL540" s="3"/>
       <c r="AM540" s="3"/>
     </row>
-    <row r="541" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -23530,7 +23530,7 @@
       <c r="AL541" s="3"/>
       <c r="AM541" s="3"/>
     </row>
-    <row r="542" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -23571,7 +23571,7 @@
       <c r="AL542" s="3"/>
       <c r="AM542" s="3"/>
     </row>
-    <row r="543" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -23612,7 +23612,7 @@
       <c r="AL543" s="3"/>
       <c r="AM543" s="3"/>
     </row>
-    <row r="544" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -23653,7 +23653,7 @@
       <c r="AL544" s="3"/>
       <c r="AM544" s="3"/>
     </row>
-    <row r="545" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -23694,7 +23694,7 @@
       <c r="AL545" s="3"/>
       <c r="AM545" s="3"/>
     </row>
-    <row r="546" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -23735,7 +23735,7 @@
       <c r="AL546" s="3"/>
       <c r="AM546" s="3"/>
     </row>
-    <row r="547" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -23776,7 +23776,7 @@
       <c r="AL547" s="3"/>
       <c r="AM547" s="3"/>
     </row>
-    <row r="548" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -23817,7 +23817,7 @@
       <c r="AL548" s="3"/>
       <c r="AM548" s="3"/>
     </row>
-    <row r="549" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -23858,7 +23858,7 @@
       <c r="AL549" s="3"/>
       <c r="AM549" s="3"/>
     </row>
-    <row r="550" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -23899,7 +23899,7 @@
       <c r="AL550" s="3"/>
       <c r="AM550" s="3"/>
     </row>
-    <row r="551" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -23940,7 +23940,7 @@
       <c r="AL551" s="3"/>
       <c r="AM551" s="3"/>
     </row>
-    <row r="552" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -23981,7 +23981,7 @@
       <c r="AL552" s="3"/>
       <c r="AM552" s="3"/>
     </row>
-    <row r="553" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -24022,7 +24022,7 @@
       <c r="AL553" s="3"/>
       <c r="AM553" s="3"/>
     </row>
-    <row r="554" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -24063,7 +24063,7 @@
       <c r="AL554" s="3"/>
       <c r="AM554" s="3"/>
     </row>
-    <row r="555" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -24104,7 +24104,7 @@
       <c r="AL555" s="3"/>
       <c r="AM555" s="3"/>
     </row>
-    <row r="556" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -24145,7 +24145,7 @@
       <c r="AL556" s="3"/>
       <c r="AM556" s="3"/>
     </row>
-    <row r="557" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -24186,7 +24186,7 @@
       <c r="AL557" s="3"/>
       <c r="AM557" s="3"/>
     </row>
-    <row r="558" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -24227,7 +24227,7 @@
       <c r="AL558" s="3"/>
       <c r="AM558" s="3"/>
     </row>
-    <row r="559" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -24268,7 +24268,7 @@
       <c r="AL559" s="3"/>
       <c r="AM559" s="3"/>
     </row>
-    <row r="560" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -24309,7 +24309,7 @@
       <c r="AL560" s="3"/>
       <c r="AM560" s="3"/>
     </row>
-    <row r="561" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -24350,7 +24350,7 @@
       <c r="AL561" s="3"/>
       <c r="AM561" s="3"/>
     </row>
-    <row r="562" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -24391,7 +24391,7 @@
       <c r="AL562" s="3"/>
       <c r="AM562" s="3"/>
     </row>
-    <row r="563" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -24432,7 +24432,7 @@
       <c r="AL563" s="3"/>
       <c r="AM563" s="3"/>
     </row>
-    <row r="564" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -24473,7 +24473,7 @@
       <c r="AL564" s="3"/>
       <c r="AM564" s="3"/>
     </row>
-    <row r="565" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -24514,7 +24514,7 @@
       <c r="AL565" s="3"/>
       <c r="AM565" s="3"/>
     </row>
-    <row r="566" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -24555,7 +24555,7 @@
       <c r="AL566" s="3"/>
       <c r="AM566" s="3"/>
     </row>
-    <row r="567" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -24596,7 +24596,7 @@
       <c r="AL567" s="3"/>
       <c r="AM567" s="3"/>
     </row>
-    <row r="568" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -24637,7 +24637,7 @@
       <c r="AL568" s="3"/>
       <c r="AM568" s="3"/>
     </row>
-    <row r="569" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -24678,7 +24678,7 @@
       <c r="AL569" s="3"/>
       <c r="AM569" s="3"/>
     </row>
-    <row r="570" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -24719,7 +24719,7 @@
       <c r="AL570" s="3"/>
       <c r="AM570" s="3"/>
     </row>
-    <row r="571" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -24760,7 +24760,7 @@
       <c r="AL571" s="3"/>
       <c r="AM571" s="3"/>
     </row>
-    <row r="572" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -24801,7 +24801,7 @@
       <c r="AL572" s="3"/>
       <c r="AM572" s="3"/>
     </row>
-    <row r="573" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -24842,7 +24842,7 @@
       <c r="AL573" s="3"/>
       <c r="AM573" s="3"/>
     </row>
-    <row r="574" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -24883,7 +24883,7 @@
       <c r="AL574" s="3"/>
       <c r="AM574" s="3"/>
     </row>
-    <row r="575" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -24924,7 +24924,7 @@
       <c r="AL575" s="3"/>
       <c r="AM575" s="3"/>
     </row>
-    <row r="576" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -24965,7 +24965,7 @@
       <c r="AL576" s="3"/>
       <c r="AM576" s="3"/>
     </row>
-    <row r="577" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -25006,7 +25006,7 @@
       <c r="AL577" s="3"/>
       <c r="AM577" s="3"/>
     </row>
-    <row r="578" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -25047,7 +25047,7 @@
       <c r="AL578" s="3"/>
       <c r="AM578" s="3"/>
     </row>
-    <row r="579" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -25088,7 +25088,7 @@
       <c r="AL579" s="3"/>
       <c r="AM579" s="3"/>
     </row>
-    <row r="580" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -25129,7 +25129,7 @@
       <c r="AL580" s="3"/>
       <c r="AM580" s="3"/>
     </row>
-    <row r="581" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -25170,7 +25170,7 @@
       <c r="AL581" s="3"/>
       <c r="AM581" s="3"/>
     </row>
-    <row r="582" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -25211,7 +25211,7 @@
       <c r="AL582" s="3"/>
       <c r="AM582" s="3"/>
     </row>
-    <row r="583" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -25252,7 +25252,7 @@
       <c r="AL583" s="3"/>
       <c r="AM583" s="3"/>
     </row>
-    <row r="584" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -25293,7 +25293,7 @@
       <c r="AL584" s="3"/>
       <c r="AM584" s="3"/>
     </row>
-    <row r="585" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -25334,7 +25334,7 @@
       <c r="AL585" s="3"/>
       <c r="AM585" s="3"/>
     </row>
-    <row r="586" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -25375,7 +25375,7 @@
       <c r="AL586" s="3"/>
       <c r="AM586" s="3"/>
     </row>
-    <row r="587" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -25416,7 +25416,7 @@
       <c r="AL587" s="3"/>
       <c r="AM587" s="3"/>
     </row>
-    <row r="588" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -25457,7 +25457,7 @@
       <c r="AL588" s="3"/>
       <c r="AM588" s="3"/>
     </row>
-    <row r="589" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -25498,7 +25498,7 @@
       <c r="AL589" s="3"/>
       <c r="AM589" s="3"/>
     </row>
-    <row r="590" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -25539,7 +25539,7 @@
       <c r="AL590" s="3"/>
       <c r="AM590" s="3"/>
     </row>
-    <row r="591" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -25580,7 +25580,7 @@
       <c r="AL591" s="3"/>
       <c r="AM591" s="3"/>
     </row>
-    <row r="592" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -25621,7 +25621,7 @@
       <c r="AL592" s="3"/>
       <c r="AM592" s="3"/>
     </row>
-    <row r="593" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -25662,7 +25662,7 @@
       <c r="AL593" s="3"/>
       <c r="AM593" s="3"/>
     </row>
-    <row r="594" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -25703,7 +25703,7 @@
       <c r="AL594" s="3"/>
       <c r="AM594" s="3"/>
     </row>
-    <row r="595" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -25744,7 +25744,7 @@
       <c r="AL595" s="3"/>
       <c r="AM595" s="3"/>
     </row>
-    <row r="596" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -25785,7 +25785,7 @@
       <c r="AL596" s="3"/>
       <c r="AM596" s="3"/>
     </row>
-    <row r="597" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -25826,7 +25826,7 @@
       <c r="AL597" s="3"/>
       <c r="AM597" s="3"/>
     </row>
-    <row r="598" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -25867,7 +25867,7 @@
       <c r="AL598" s="3"/>
       <c r="AM598" s="3"/>
     </row>
-    <row r="599" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -25908,7 +25908,7 @@
       <c r="AL599" s="3"/>
       <c r="AM599" s="3"/>
     </row>
-    <row r="600" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -25949,7 +25949,7 @@
       <c r="AL600" s="3"/>
       <c r="AM600" s="3"/>
     </row>
-    <row r="601" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -25990,7 +25990,7 @@
       <c r="AL601" s="3"/>
       <c r="AM601" s="3"/>
     </row>
-    <row r="602" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -26031,7 +26031,7 @@
       <c r="AL602" s="3"/>
       <c r="AM602" s="3"/>
     </row>
-    <row r="603" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -26072,7 +26072,7 @@
       <c r="AL603" s="3"/>
       <c r="AM603" s="3"/>
     </row>
-    <row r="604" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -26113,7 +26113,7 @@
       <c r="AL604" s="3"/>
       <c r="AM604" s="3"/>
     </row>
-    <row r="605" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -26154,7 +26154,7 @@
       <c r="AL605" s="3"/>
       <c r="AM605" s="3"/>
     </row>
-    <row r="606" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -26195,7 +26195,7 @@
       <c r="AL606" s="3"/>
       <c r="AM606" s="3"/>
     </row>
-    <row r="607" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -26236,7 +26236,7 @@
       <c r="AL607" s="3"/>
       <c r="AM607" s="3"/>
     </row>
-    <row r="608" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -26277,7 +26277,7 @@
       <c r="AL608" s="3"/>
       <c r="AM608" s="3"/>
     </row>
-    <row r="609" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -26318,7 +26318,7 @@
       <c r="AL609" s="3"/>
       <c r="AM609" s="3"/>
     </row>
-    <row r="610" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -26359,7 +26359,7 @@
       <c r="AL610" s="3"/>
       <c r="AM610" s="3"/>
     </row>
-    <row r="611" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -26400,7 +26400,7 @@
       <c r="AL611" s="3"/>
       <c r="AM611" s="3"/>
     </row>
-    <row r="612" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -26441,7 +26441,7 @@
       <c r="AL612" s="3"/>
       <c r="AM612" s="3"/>
     </row>
-    <row r="613" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -26482,7 +26482,7 @@
       <c r="AL613" s="3"/>
       <c r="AM613" s="3"/>
     </row>
-    <row r="614" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -26523,7 +26523,7 @@
       <c r="AL614" s="3"/>
       <c r="AM614" s="3"/>
     </row>
-    <row r="615" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -26564,7 +26564,7 @@
       <c r="AL615" s="3"/>
       <c r="AM615" s="3"/>
     </row>
-    <row r="616" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -26605,7 +26605,7 @@
       <c r="AL616" s="3"/>
       <c r="AM616" s="3"/>
     </row>
-    <row r="617" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -26646,7 +26646,7 @@
       <c r="AL617" s="3"/>
       <c r="AM617" s="3"/>
     </row>
-    <row r="618" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -26687,7 +26687,7 @@
       <c r="AL618" s="3"/>
       <c r="AM618" s="3"/>
     </row>
-    <row r="619" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -26728,7 +26728,7 @@
       <c r="AL619" s="3"/>
       <c r="AM619" s="3"/>
     </row>
-    <row r="620" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -26769,7 +26769,7 @@
       <c r="AL620" s="3"/>
       <c r="AM620" s="3"/>
     </row>
-    <row r="621" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -26810,7 +26810,7 @@
       <c r="AL621" s="3"/>
       <c r="AM621" s="3"/>
     </row>
-    <row r="622" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -26851,7 +26851,7 @@
       <c r="AL622" s="3"/>
       <c r="AM622" s="3"/>
     </row>
-    <row r="623" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -26892,7 +26892,7 @@
       <c r="AL623" s="3"/>
       <c r="AM623" s="3"/>
     </row>
-    <row r="624" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -26933,7 +26933,7 @@
       <c r="AL624" s="3"/>
       <c r="AM624" s="3"/>
     </row>
-    <row r="625" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -26974,7 +26974,7 @@
       <c r="AL625" s="3"/>
       <c r="AM625" s="3"/>
     </row>
-    <row r="626" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -27015,7 +27015,7 @@
       <c r="AL626" s="3"/>
       <c r="AM626" s="3"/>
     </row>
-    <row r="627" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -27056,7 +27056,7 @@
       <c r="AL627" s="3"/>
       <c r="AM627" s="3"/>
     </row>
-    <row r="628" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -27097,7 +27097,7 @@
       <c r="AL628" s="3"/>
       <c r="AM628" s="3"/>
     </row>
-    <row r="629" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -27138,7 +27138,7 @@
       <c r="AL629" s="3"/>
       <c r="AM629" s="3"/>
     </row>
-    <row r="630" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -27179,7 +27179,7 @@
       <c r="AL630" s="3"/>
       <c r="AM630" s="3"/>
     </row>
-    <row r="631" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -27220,7 +27220,7 @@
       <c r="AL631" s="3"/>
       <c r="AM631" s="3"/>
     </row>
-    <row r="632" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -27261,7 +27261,7 @@
       <c r="AL632" s="3"/>
       <c r="AM632" s="3"/>
     </row>
-    <row r="633" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -27302,7 +27302,7 @@
       <c r="AL633" s="3"/>
       <c r="AM633" s="3"/>
     </row>
-    <row r="634" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -27343,7 +27343,7 @@
       <c r="AL634" s="3"/>
       <c r="AM634" s="3"/>
     </row>
-    <row r="635" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -27384,7 +27384,7 @@
       <c r="AL635" s="3"/>
       <c r="AM635" s="3"/>
     </row>
-    <row r="636" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -27425,7 +27425,7 @@
       <c r="AL636" s="3"/>
       <c r="AM636" s="3"/>
     </row>
-    <row r="637" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -27466,7 +27466,7 @@
       <c r="AL637" s="3"/>
       <c r="AM637" s="3"/>
     </row>
-    <row r="638" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -27507,7 +27507,7 @@
       <c r="AL638" s="3"/>
       <c r="AM638" s="3"/>
     </row>
-    <row r="639" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -27548,7 +27548,7 @@
       <c r="AL639" s="3"/>
       <c r="AM639" s="3"/>
     </row>
-    <row r="640" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -27589,7 +27589,7 @@
       <c r="AL640" s="3"/>
       <c r="AM640" s="3"/>
     </row>
-    <row r="641" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -27630,7 +27630,7 @@
       <c r="AL641" s="3"/>
       <c r="AM641" s="3"/>
     </row>
-    <row r="642" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -27671,7 +27671,7 @@
       <c r="AL642" s="3"/>
       <c r="AM642" s="3"/>
     </row>
-    <row r="643" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -27712,7 +27712,7 @@
       <c r="AL643" s="3"/>
       <c r="AM643" s="3"/>
     </row>
-    <row r="644" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -27753,7 +27753,7 @@
       <c r="AL644" s="3"/>
       <c r="AM644" s="3"/>
     </row>
-    <row r="645" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -27794,7 +27794,7 @@
       <c r="AL645" s="3"/>
       <c r="AM645" s="3"/>
     </row>
-    <row r="646" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -27835,7 +27835,7 @@
       <c r="AL646" s="3"/>
       <c r="AM646" s="3"/>
     </row>
-    <row r="647" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -27876,7 +27876,7 @@
       <c r="AL647" s="3"/>
       <c r="AM647" s="3"/>
     </row>
-    <row r="648" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -27917,7 +27917,7 @@
       <c r="AL648" s="3"/>
       <c r="AM648" s="3"/>
     </row>
-    <row r="649" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -27958,7 +27958,7 @@
       <c r="AL649" s="3"/>
       <c r="AM649" s="3"/>
     </row>
-    <row r="650" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -27999,7 +27999,7 @@
       <c r="AL650" s="3"/>
       <c r="AM650" s="3"/>
     </row>
-    <row r="651" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -28040,7 +28040,7 @@
       <c r="AL651" s="3"/>
       <c r="AM651" s="3"/>
     </row>
-    <row r="652" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -28081,7 +28081,7 @@
       <c r="AL652" s="3"/>
       <c r="AM652" s="3"/>
     </row>
-    <row r="653" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -28122,7 +28122,7 @@
       <c r="AL653" s="3"/>
       <c r="AM653" s="3"/>
     </row>
-    <row r="654" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -28163,7 +28163,7 @@
       <c r="AL654" s="3"/>
       <c r="AM654" s="3"/>
     </row>
-    <row r="655" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -28204,7 +28204,7 @@
       <c r="AL655" s="3"/>
       <c r="AM655" s="3"/>
     </row>
-    <row r="656" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -28245,7 +28245,7 @@
       <c r="AL656" s="3"/>
       <c r="AM656" s="3"/>
     </row>
-    <row r="657" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -28286,7 +28286,7 @@
       <c r="AL657" s="3"/>
       <c r="AM657" s="3"/>
     </row>
-    <row r="658" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -28327,7 +28327,7 @@
       <c r="AL658" s="3"/>
       <c r="AM658" s="3"/>
     </row>
-    <row r="659" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -28368,7 +28368,7 @@
       <c r="AL659" s="3"/>
       <c r="AM659" s="3"/>
     </row>
-    <row r="660" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -28409,7 +28409,7 @@
       <c r="AL660" s="3"/>
       <c r="AM660" s="3"/>
     </row>
-    <row r="661" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -28450,7 +28450,7 @@
       <c r="AL661" s="3"/>
       <c r="AM661" s="3"/>
     </row>
-    <row r="662" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -28491,7 +28491,7 @@
       <c r="AL662" s="3"/>
       <c r="AM662" s="3"/>
     </row>
-    <row r="663" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -28532,7 +28532,7 @@
       <c r="AL663" s="3"/>
       <c r="AM663" s="3"/>
     </row>
-    <row r="664" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -28573,7 +28573,7 @@
       <c r="AL664" s="3"/>
       <c r="AM664" s="3"/>
     </row>
-    <row r="665" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -28614,7 +28614,7 @@
       <c r="AL665" s="3"/>
       <c r="AM665" s="3"/>
     </row>
-    <row r="666" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -28655,7 +28655,7 @@
       <c r="AL666" s="3"/>
       <c r="AM666" s="3"/>
     </row>
-    <row r="667" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -28696,7 +28696,7 @@
       <c r="AL667" s="3"/>
       <c r="AM667" s="3"/>
     </row>
-    <row r="668" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -28737,7 +28737,7 @@
       <c r="AL668" s="3"/>
       <c r="AM668" s="3"/>
     </row>
-    <row r="669" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -28778,7 +28778,7 @@
       <c r="AL669" s="3"/>
       <c r="AM669" s="3"/>
     </row>
-    <row r="670" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -28819,7 +28819,7 @@
       <c r="AL670" s="3"/>
       <c r="AM670" s="3"/>
     </row>
-    <row r="671" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -28860,7 +28860,7 @@
       <c r="AL671" s="3"/>
       <c r="AM671" s="3"/>
     </row>
-    <row r="672" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -28901,7 +28901,7 @@
       <c r="AL672" s="3"/>
       <c r="AM672" s="3"/>
     </row>
-    <row r="673" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -28942,7 +28942,7 @@
       <c r="AL673" s="3"/>
       <c r="AM673" s="3"/>
     </row>
-    <row r="674" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -28983,7 +28983,7 @@
       <c r="AL674" s="3"/>
       <c r="AM674" s="3"/>
     </row>
-    <row r="675" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -29024,7 +29024,7 @@
       <c r="AL675" s="3"/>
       <c r="AM675" s="3"/>
     </row>
-    <row r="676" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -29065,7 +29065,7 @@
       <c r="AL676" s="3"/>
       <c r="AM676" s="3"/>
     </row>
-    <row r="677" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -29106,7 +29106,7 @@
       <c r="AL677" s="3"/>
       <c r="AM677" s="3"/>
     </row>
-    <row r="678" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -29147,7 +29147,7 @@
       <c r="AL678" s="3"/>
       <c r="AM678" s="3"/>
     </row>
-    <row r="679" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -29188,7 +29188,7 @@
       <c r="AL679" s="3"/>
       <c r="AM679" s="3"/>
     </row>
-    <row r="680" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -29229,7 +29229,7 @@
       <c r="AL680" s="3"/>
       <c r="AM680" s="3"/>
     </row>
-    <row r="681" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -29270,7 +29270,7 @@
       <c r="AL681" s="3"/>
       <c r="AM681" s="3"/>
     </row>
-    <row r="682" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -29311,7 +29311,7 @@
       <c r="AL682" s="3"/>
       <c r="AM682" s="3"/>
     </row>
-    <row r="683" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -29352,7 +29352,7 @@
       <c r="AL683" s="3"/>
       <c r="AM683" s="3"/>
     </row>
-    <row r="684" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -29393,7 +29393,7 @@
       <c r="AL684" s="3"/>
       <c r="AM684" s="3"/>
     </row>
-    <row r="685" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -29434,7 +29434,7 @@
       <c r="AL685" s="3"/>
       <c r="AM685" s="3"/>
     </row>
-    <row r="686" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -29475,7 +29475,7 @@
       <c r="AL686" s="3"/>
       <c r="AM686" s="3"/>
     </row>
-    <row r="687" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -29516,7 +29516,7 @@
       <c r="AL687" s="3"/>
       <c r="AM687" s="3"/>
     </row>
-    <row r="688" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -29557,7 +29557,7 @@
       <c r="AL688" s="3"/>
       <c r="AM688" s="3"/>
     </row>
-    <row r="689" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -29598,7 +29598,7 @@
       <c r="AL689" s="3"/>
       <c r="AM689" s="3"/>
     </row>
-    <row r="690" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -29639,7 +29639,7 @@
       <c r="AL690" s="3"/>
       <c r="AM690" s="3"/>
     </row>
-    <row r="691" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -29680,7 +29680,7 @@
       <c r="AL691" s="3"/>
       <c r="AM691" s="3"/>
     </row>
-    <row r="692" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -29721,7 +29721,7 @@
       <c r="AL692" s="3"/>
       <c r="AM692" s="3"/>
     </row>
-    <row r="693" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -29762,7 +29762,7 @@
       <c r="AL693" s="3"/>
       <c r="AM693" s="3"/>
     </row>
-    <row r="694" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -29803,7 +29803,7 @@
       <c r="AL694" s="3"/>
       <c r="AM694" s="3"/>
     </row>
-    <row r="695" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -29844,7 +29844,7 @@
       <c r="AL695" s="3"/>
       <c r="AM695" s="3"/>
     </row>
-    <row r="696" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -29885,7 +29885,7 @@
       <c r="AL696" s="3"/>
       <c r="AM696" s="3"/>
     </row>
-    <row r="697" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -29926,7 +29926,7 @@
       <c r="AL697" s="3"/>
       <c r="AM697" s="3"/>
     </row>
-    <row r="698" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -29967,7 +29967,7 @@
       <c r="AL698" s="3"/>
       <c r="AM698" s="3"/>
     </row>
-    <row r="699" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -30008,7 +30008,7 @@
       <c r="AL699" s="3"/>
       <c r="AM699" s="3"/>
     </row>
-    <row r="700" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -30049,7 +30049,7 @@
       <c r="AL700" s="3"/>
       <c r="AM700" s="3"/>
     </row>
-    <row r="701" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -30090,7 +30090,7 @@
       <c r="AL701" s="3"/>
       <c r="AM701" s="3"/>
     </row>
-    <row r="702" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -30131,7 +30131,7 @@
       <c r="AL702" s="3"/>
       <c r="AM702" s="3"/>
     </row>
-    <row r="703" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -30172,7 +30172,7 @@
       <c r="AL703" s="3"/>
       <c r="AM703" s="3"/>
     </row>
-    <row r="704" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -30213,7 +30213,7 @@
       <c r="AL704" s="3"/>
       <c r="AM704" s="3"/>
     </row>
-    <row r="705" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -30254,7 +30254,7 @@
       <c r="AL705" s="3"/>
       <c r="AM705" s="3"/>
     </row>
-    <row r="706" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -30295,7 +30295,7 @@
       <c r="AL706" s="3"/>
       <c r="AM706" s="3"/>
     </row>
-    <row r="707" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -30336,7 +30336,7 @@
       <c r="AL707" s="3"/>
       <c r="AM707" s="3"/>
     </row>
-    <row r="708" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -30377,7 +30377,7 @@
       <c r="AL708" s="3"/>
       <c r="AM708" s="3"/>
     </row>
-    <row r="709" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -30418,7 +30418,7 @@
       <c r="AL709" s="3"/>
       <c r="AM709" s="3"/>
     </row>
-    <row r="710" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -30459,7 +30459,7 @@
       <c r="AL710" s="3"/>
       <c r="AM710" s="3"/>
     </row>
-    <row r="711" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -30500,7 +30500,7 @@
       <c r="AL711" s="3"/>
       <c r="AM711" s="3"/>
     </row>
-    <row r="712" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -30541,7 +30541,7 @@
       <c r="AL712" s="3"/>
       <c r="AM712" s="3"/>
     </row>
-    <row r="713" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -30582,7 +30582,7 @@
       <c r="AL713" s="3"/>
       <c r="AM713" s="3"/>
     </row>
-    <row r="714" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -30623,7 +30623,7 @@
       <c r="AL714" s="3"/>
       <c r="AM714" s="3"/>
     </row>
-    <row r="715" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -30664,7 +30664,7 @@
       <c r="AL715" s="3"/>
       <c r="AM715" s="3"/>
     </row>
-    <row r="716" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -30705,7 +30705,7 @@
       <c r="AL716" s="3"/>
       <c r="AM716" s="3"/>
     </row>
-    <row r="717" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -30746,7 +30746,7 @@
       <c r="AL717" s="3"/>
       <c r="AM717" s="3"/>
     </row>
-    <row r="718" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -30787,7 +30787,7 @@
       <c r="AL718" s="3"/>
       <c r="AM718" s="3"/>
     </row>
-    <row r="719" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -30828,7 +30828,7 @@
       <c r="AL719" s="3"/>
       <c r="AM719" s="3"/>
     </row>
-    <row r="720" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -30869,7 +30869,7 @@
       <c r="AL720" s="3"/>
       <c r="AM720" s="3"/>
     </row>
-    <row r="721" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -30910,7 +30910,7 @@
       <c r="AL721" s="3"/>
       <c r="AM721" s="3"/>
     </row>
-    <row r="722" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -30951,7 +30951,7 @@
       <c r="AL722" s="3"/>
       <c r="AM722" s="3"/>
     </row>
-    <row r="723" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -30992,7 +30992,7 @@
       <c r="AL723" s="3"/>
       <c r="AM723" s="3"/>
     </row>
-    <row r="724" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -31033,7 +31033,7 @@
       <c r="AL724" s="3"/>
       <c r="AM724" s="3"/>
     </row>
-    <row r="725" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -31074,7 +31074,7 @@
       <c r="AL725" s="3"/>
       <c r="AM725" s="3"/>
     </row>
-    <row r="726" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -31115,7 +31115,7 @@
       <c r="AL726" s="3"/>
       <c r="AM726" s="3"/>
     </row>
-    <row r="727" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -31156,7 +31156,7 @@
       <c r="AL727" s="3"/>
       <c r="AM727" s="3"/>
     </row>
-    <row r="728" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -31197,7 +31197,7 @@
       <c r="AL728" s="3"/>
       <c r="AM728" s="3"/>
     </row>
-    <row r="729" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -31238,7 +31238,7 @@
       <c r="AL729" s="3"/>
       <c r="AM729" s="3"/>
     </row>
-    <row r="730" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -31279,7 +31279,7 @@
       <c r="AL730" s="3"/>
       <c r="AM730" s="3"/>
     </row>
-    <row r="731" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -31320,7 +31320,7 @@
       <c r="AL731" s="3"/>
       <c r="AM731" s="3"/>
     </row>
-    <row r="732" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -31361,7 +31361,7 @@
       <c r="AL732" s="3"/>
       <c r="AM732" s="3"/>
     </row>
-    <row r="733" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -31402,7 +31402,7 @@
       <c r="AL733" s="3"/>
       <c r="AM733" s="3"/>
     </row>
-    <row r="734" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -31443,7 +31443,7 @@
       <c r="AL734" s="3"/>
       <c r="AM734" s="3"/>
     </row>
-    <row r="735" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -31484,7 +31484,7 @@
       <c r="AL735" s="3"/>
       <c r="AM735" s="3"/>
     </row>
-    <row r="736" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -31525,7 +31525,7 @@
       <c r="AL736" s="3"/>
       <c r="AM736" s="3"/>
     </row>
-    <row r="737" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -31566,7 +31566,7 @@
       <c r="AL737" s="3"/>
       <c r="AM737" s="3"/>
     </row>
-    <row r="738" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -31607,7 +31607,7 @@
       <c r="AL738" s="3"/>
       <c r="AM738" s="3"/>
     </row>
-    <row r="739" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -31648,7 +31648,7 @@
       <c r="AL739" s="3"/>
       <c r="AM739" s="3"/>
     </row>
-    <row r="740" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -31689,7 +31689,7 @@
       <c r="AL740" s="3"/>
       <c r="AM740" s="3"/>
     </row>
-    <row r="741" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -31730,7 +31730,7 @@
       <c r="AL741" s="3"/>
       <c r="AM741" s="3"/>
     </row>
-    <row r="742" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -31771,7 +31771,7 @@
       <c r="AL742" s="3"/>
       <c r="AM742" s="3"/>
     </row>
-    <row r="743" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -31812,7 +31812,7 @@
       <c r="AL743" s="3"/>
       <c r="AM743" s="3"/>
     </row>
-    <row r="744" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -31853,7 +31853,7 @@
       <c r="AL744" s="3"/>
       <c r="AM744" s="3"/>
     </row>
-    <row r="745" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -31894,7 +31894,7 @@
       <c r="AL745" s="3"/>
       <c r="AM745" s="3"/>
     </row>
-    <row r="746" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -31935,7 +31935,7 @@
       <c r="AL746" s="3"/>
       <c r="AM746" s="3"/>
     </row>
-    <row r="747" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -31976,7 +31976,7 @@
       <c r="AL747" s="3"/>
       <c r="AM747" s="3"/>
     </row>
-    <row r="748" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -32017,7 +32017,7 @@
       <c r="AL748" s="3"/>
       <c r="AM748" s="3"/>
     </row>
-    <row r="749" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -32058,7 +32058,7 @@
       <c r="AL749" s="3"/>
       <c r="AM749" s="3"/>
     </row>
-    <row r="750" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -32099,7 +32099,7 @@
       <c r="AL750" s="3"/>
       <c r="AM750" s="3"/>
     </row>
-    <row r="751" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -32140,7 +32140,7 @@
       <c r="AL751" s="3"/>
       <c r="AM751" s="3"/>
     </row>
-    <row r="752" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -32181,7 +32181,7 @@
       <c r="AL752" s="3"/>
       <c r="AM752" s="3"/>
     </row>
-    <row r="753" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -32222,7 +32222,7 @@
       <c r="AL753" s="3"/>
       <c r="AM753" s="3"/>
     </row>
-    <row r="754" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -32263,7 +32263,7 @@
       <c r="AL754" s="3"/>
       <c r="AM754" s="3"/>
     </row>
-    <row r="755" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -32304,7 +32304,7 @@
       <c r="AL755" s="3"/>
       <c r="AM755" s="3"/>
     </row>
-    <row r="756" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -32345,7 +32345,7 @@
       <c r="AL756" s="3"/>
       <c r="AM756" s="3"/>
     </row>
-    <row r="757" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -32386,7 +32386,7 @@
       <c r="AL757" s="3"/>
       <c r="AM757" s="3"/>
     </row>
-    <row r="758" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -32427,7 +32427,7 @@
       <c r="AL758" s="3"/>
       <c r="AM758" s="3"/>
     </row>
-    <row r="759" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -32468,7 +32468,7 @@
       <c r="AL759" s="3"/>
       <c r="AM759" s="3"/>
     </row>
-    <row r="760" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -32509,7 +32509,7 @@
       <c r="AL760" s="3"/>
       <c r="AM760" s="3"/>
     </row>
-    <row r="761" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -32550,7 +32550,7 @@
       <c r="AL761" s="3"/>
       <c r="AM761" s="3"/>
     </row>
-    <row r="762" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -32591,7 +32591,7 @@
       <c r="AL762" s="3"/>
       <c r="AM762" s="3"/>
     </row>
-    <row r="763" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -32632,7 +32632,7 @@
       <c r="AL763" s="3"/>
       <c r="AM763" s="3"/>
     </row>
-    <row r="764" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -32673,7 +32673,7 @@
       <c r="AL764" s="3"/>
       <c r="AM764" s="3"/>
     </row>
-    <row r="765" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -32714,7 +32714,7 @@
       <c r="AL765" s="3"/>
       <c r="AM765" s="3"/>
     </row>
-    <row r="766" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -32755,7 +32755,7 @@
       <c r="AL766" s="3"/>
       <c r="AM766" s="3"/>
     </row>
-    <row r="767" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -32796,7 +32796,7 @@
       <c r="AL767" s="3"/>
       <c r="AM767" s="3"/>
     </row>
-    <row r="768" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -32837,7 +32837,7 @@
       <c r="AL768" s="3"/>
       <c r="AM768" s="3"/>
     </row>
-    <row r="769" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -32878,7 +32878,7 @@
       <c r="AL769" s="3"/>
       <c r="AM769" s="3"/>
     </row>
-    <row r="770" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -32919,7 +32919,7 @@
       <c r="AL770" s="3"/>
       <c r="AM770" s="3"/>
     </row>
-    <row r="771" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -32960,7 +32960,7 @@
       <c r="AL771" s="3"/>
       <c r="AM771" s="3"/>
     </row>
-    <row r="772" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -33001,7 +33001,7 @@
       <c r="AL772" s="3"/>
       <c r="AM772" s="3"/>
     </row>
-    <row r="773" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -33042,7 +33042,7 @@
       <c r="AL773" s="3"/>
       <c r="AM773" s="3"/>
     </row>
-    <row r="774" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -33083,7 +33083,7 @@
       <c r="AL774" s="3"/>
       <c r="AM774" s="3"/>
     </row>
-    <row r="775" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -33124,7 +33124,7 @@
       <c r="AL775" s="3"/>
       <c r="AM775" s="3"/>
     </row>
-    <row r="776" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -33165,7 +33165,7 @@
       <c r="AL776" s="3"/>
       <c r="AM776" s="3"/>
     </row>
-    <row r="777" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -33206,7 +33206,7 @@
       <c r="AL777" s="3"/>
       <c r="AM777" s="3"/>
     </row>
-    <row r="778" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -33247,7 +33247,7 @@
       <c r="AL778" s="3"/>
       <c r="AM778" s="3"/>
     </row>
-    <row r="779" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -33288,7 +33288,7 @@
       <c r="AL779" s="3"/>
       <c r="AM779" s="3"/>
     </row>
-    <row r="780" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -33329,7 +33329,7 @@
       <c r="AL780" s="3"/>
       <c r="AM780" s="3"/>
     </row>
-    <row r="781" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -33370,7 +33370,7 @@
       <c r="AL781" s="3"/>
       <c r="AM781" s="3"/>
     </row>
-    <row r="782" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -33411,7 +33411,7 @@
       <c r="AL782" s="3"/>
       <c r="AM782" s="3"/>
     </row>
-    <row r="783" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -33452,7 +33452,7 @@
       <c r="AL783" s="3"/>
       <c r="AM783" s="3"/>
     </row>
-    <row r="784" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -33493,7 +33493,7 @@
       <c r="AL784" s="3"/>
       <c r="AM784" s="3"/>
     </row>
-    <row r="785" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -33534,7 +33534,7 @@
       <c r="AL785" s="3"/>
       <c r="AM785" s="3"/>
     </row>
-    <row r="786" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -33575,7 +33575,7 @@
       <c r="AL786" s="3"/>
       <c r="AM786" s="3"/>
     </row>
-    <row r="787" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -33616,7 +33616,7 @@
       <c r="AL787" s="3"/>
       <c r="AM787" s="3"/>
     </row>
-    <row r="788" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -33657,7 +33657,7 @@
       <c r="AL788" s="3"/>
       <c r="AM788" s="3"/>
     </row>
-    <row r="789" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -33698,7 +33698,7 @@
       <c r="AL789" s="3"/>
       <c r="AM789" s="3"/>
     </row>
-    <row r="790" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -33739,7 +33739,7 @@
       <c r="AL790" s="3"/>
       <c r="AM790" s="3"/>
     </row>
-    <row r="791" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -33780,7 +33780,7 @@
       <c r="AL791" s="3"/>
       <c r="AM791" s="3"/>
     </row>
-    <row r="792" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -33821,7 +33821,7 @@
       <c r="AL792" s="3"/>
       <c r="AM792" s="3"/>
     </row>
-    <row r="793" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -33862,7 +33862,7 @@
       <c r="AL793" s="3"/>
       <c r="AM793" s="3"/>
     </row>
-    <row r="794" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -33903,7 +33903,7 @@
       <c r="AL794" s="3"/>
       <c r="AM794" s="3"/>
     </row>
-    <row r="795" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -33944,7 +33944,7 @@
       <c r="AL795" s="3"/>
       <c r="AM795" s="3"/>
     </row>
-    <row r="796" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -33985,7 +33985,7 @@
       <c r="AL796" s="3"/>
       <c r="AM796" s="3"/>
     </row>
-    <row r="797" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -34026,7 +34026,7 @@
       <c r="AL797" s="3"/>
       <c r="AM797" s="3"/>
     </row>
-    <row r="798" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -34067,7 +34067,7 @@
       <c r="AL798" s="3"/>
       <c r="AM798" s="3"/>
     </row>
-    <row r="799" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -34108,7 +34108,7 @@
       <c r="AL799" s="3"/>
       <c r="AM799" s="3"/>
     </row>
-    <row r="800" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -34149,7 +34149,7 @@
       <c r="AL800" s="3"/>
       <c r="AM800" s="3"/>
     </row>
-    <row r="801" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -34190,7 +34190,7 @@
       <c r="AL801" s="3"/>
       <c r="AM801" s="3"/>
     </row>
-    <row r="802" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -34231,7 +34231,7 @@
       <c r="AL802" s="3"/>
       <c r="AM802" s="3"/>
     </row>
-    <row r="803" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -34272,7 +34272,7 @@
       <c r="AL803" s="3"/>
       <c r="AM803" s="3"/>
     </row>
-    <row r="804" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -34313,7 +34313,7 @@
       <c r="AL804" s="3"/>
       <c r="AM804" s="3"/>
     </row>
-    <row r="805" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -34354,7 +34354,7 @@
       <c r="AL805" s="3"/>
       <c r="AM805" s="3"/>
     </row>
-    <row r="806" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -34395,7 +34395,7 @@
       <c r="AL806" s="3"/>
       <c r="AM806" s="3"/>
     </row>
-    <row r="807" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -34436,7 +34436,7 @@
       <c r="AL807" s="3"/>
       <c r="AM807" s="3"/>
     </row>
-    <row r="808" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -34477,7 +34477,7 @@
       <c r="AL808" s="3"/>
       <c r="AM808" s="3"/>
     </row>
-    <row r="809" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -34518,7 +34518,7 @@
       <c r="AL809" s="3"/>
       <c r="AM809" s="3"/>
     </row>
-    <row r="810" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -34559,7 +34559,7 @@
       <c r="AL810" s="3"/>
       <c r="AM810" s="3"/>
     </row>
-    <row r="811" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -34600,7 +34600,7 @@
       <c r="AL811" s="3"/>
       <c r="AM811" s="3"/>
     </row>
-    <row r="812" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -34641,7 +34641,7 @@
       <c r="AL812" s="3"/>
       <c r="AM812" s="3"/>
     </row>
-    <row r="813" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -34682,7 +34682,7 @@
       <c r="AL813" s="3"/>
       <c r="AM813" s="3"/>
     </row>
-    <row r="814" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -34723,7 +34723,7 @@
       <c r="AL814" s="3"/>
       <c r="AM814" s="3"/>
     </row>
-    <row r="815" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -34764,7 +34764,7 @@
       <c r="AL815" s="3"/>
       <c r="AM815" s="3"/>
     </row>
-    <row r="816" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -34805,7 +34805,7 @@
       <c r="AL816" s="3"/>
       <c r="AM816" s="3"/>
     </row>
-    <row r="817" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -34846,7 +34846,7 @@
       <c r="AL817" s="3"/>
       <c r="AM817" s="3"/>
     </row>
-    <row r="818" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -34887,7 +34887,7 @@
       <c r="AL818" s="3"/>
       <c r="AM818" s="3"/>
     </row>
-    <row r="819" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -34928,7 +34928,7 @@
       <c r="AL819" s="3"/>
       <c r="AM819" s="3"/>
     </row>
-    <row r="820" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -34969,7 +34969,7 @@
       <c r="AL820" s="3"/>
       <c r="AM820" s="3"/>
     </row>
-    <row r="821" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -35010,7 +35010,7 @@
       <c r="AL821" s="3"/>
       <c r="AM821" s="3"/>
     </row>
-    <row r="822" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -35051,7 +35051,7 @@
       <c r="AL822" s="3"/>
       <c r="AM822" s="3"/>
     </row>
-    <row r="823" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -35092,7 +35092,7 @@
       <c r="AL823" s="3"/>
       <c r="AM823" s="3"/>
     </row>
-    <row r="824" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -35133,7 +35133,7 @@
       <c r="AL824" s="3"/>
       <c r="AM824" s="3"/>
     </row>
-    <row r="825" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -35174,7 +35174,7 @@
       <c r="AL825" s="3"/>
       <c r="AM825" s="3"/>
     </row>
-    <row r="826" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -35215,7 +35215,7 @@
       <c r="AL826" s="3"/>
       <c r="AM826" s="3"/>
     </row>
-    <row r="827" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -35256,7 +35256,7 @@
       <c r="AL827" s="3"/>
       <c r="AM827" s="3"/>
     </row>
-    <row r="828" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -35297,7 +35297,7 @@
       <c r="AL828" s="3"/>
       <c r="AM828" s="3"/>
     </row>
-    <row r="829" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -35338,7 +35338,7 @@
       <c r="AL829" s="3"/>
       <c r="AM829" s="3"/>
     </row>
-    <row r="830" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -35379,7 +35379,7 @@
       <c r="AL830" s="3"/>
       <c r="AM830" s="3"/>
     </row>
-    <row r="831" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -35420,7 +35420,7 @@
       <c r="AL831" s="3"/>
       <c r="AM831" s="3"/>
     </row>
-    <row r="832" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -35461,7 +35461,7 @@
       <c r="AL832" s="3"/>
       <c r="AM832" s="3"/>
     </row>
-    <row r="833" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -35502,7 +35502,7 @@
       <c r="AL833" s="3"/>
       <c r="AM833" s="3"/>
     </row>
-    <row r="834" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -35543,7 +35543,7 @@
       <c r="AL834" s="3"/>
       <c r="AM834" s="3"/>
     </row>
-    <row r="835" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -35584,7 +35584,7 @@
       <c r="AL835" s="3"/>
       <c r="AM835" s="3"/>
     </row>
-    <row r="836" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -35625,7 +35625,7 @@
       <c r="AL836" s="3"/>
       <c r="AM836" s="3"/>
     </row>
-    <row r="837" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -35666,7 +35666,7 @@
       <c r="AL837" s="3"/>
       <c r="AM837" s="3"/>
     </row>
-    <row r="838" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -35707,7 +35707,7 @@
       <c r="AL838" s="3"/>
       <c r="AM838" s="3"/>
     </row>
-    <row r="839" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -35748,7 +35748,7 @@
       <c r="AL839" s="3"/>
       <c r="AM839" s="3"/>
     </row>
-    <row r="840" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -35789,7 +35789,7 @@
       <c r="AL840" s="3"/>
       <c r="AM840" s="3"/>
     </row>
-    <row r="841" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -35830,7 +35830,7 @@
       <c r="AL841" s="3"/>
       <c r="AM841" s="3"/>
     </row>
-    <row r="842" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -35871,7 +35871,7 @@
       <c r="AL842" s="3"/>
       <c r="AM842" s="3"/>
     </row>
-    <row r="843" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -35912,7 +35912,7 @@
       <c r="AL843" s="3"/>
       <c r="AM843" s="3"/>
     </row>
-    <row r="844" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -35953,7 +35953,7 @@
       <c r="AL844" s="3"/>
       <c r="AM844" s="3"/>
     </row>
-    <row r="845" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -35994,7 +35994,7 @@
       <c r="AL845" s="3"/>
       <c r="AM845" s="3"/>
     </row>
-    <row r="846" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -36035,7 +36035,7 @@
       <c r="AL846" s="3"/>
       <c r="AM846" s="3"/>
     </row>
-    <row r="847" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -36076,7 +36076,7 @@
       <c r="AL847" s="3"/>
       <c r="AM847" s="3"/>
     </row>
-    <row r="848" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -36117,7 +36117,7 @@
       <c r="AL848" s="3"/>
       <c r="AM848" s="3"/>
     </row>
-    <row r="849" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -36158,7 +36158,7 @@
       <c r="AL849" s="3"/>
       <c r="AM849" s="3"/>
     </row>
-    <row r="850" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -36199,7 +36199,7 @@
       <c r="AL850" s="3"/>
       <c r="AM850" s="3"/>
     </row>
-    <row r="851" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -36240,7 +36240,7 @@
       <c r="AL851" s="3"/>
       <c r="AM851" s="3"/>
     </row>
-    <row r="852" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -36281,7 +36281,7 @@
       <c r="AL852" s="3"/>
       <c r="AM852" s="3"/>
     </row>
-    <row r="853" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -36322,7 +36322,7 @@
       <c r="AL853" s="3"/>
       <c r="AM853" s="3"/>
     </row>
-    <row r="854" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -36363,7 +36363,7 @@
       <c r="AL854" s="3"/>
       <c r="AM854" s="3"/>
     </row>
-    <row r="855" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -36404,7 +36404,7 @@
       <c r="AL855" s="3"/>
       <c r="AM855" s="3"/>
     </row>
-    <row r="856" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -36445,7 +36445,7 @@
       <c r="AL856" s="3"/>
       <c r="AM856" s="3"/>
     </row>
-    <row r="857" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -36486,7 +36486,7 @@
       <c r="AL857" s="3"/>
       <c r="AM857" s="3"/>
     </row>
-    <row r="858" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -36527,7 +36527,7 @@
       <c r="AL858" s="3"/>
       <c r="AM858" s="3"/>
     </row>
-    <row r="859" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -36568,7 +36568,7 @@
       <c r="AL859" s="3"/>
       <c r="AM859" s="3"/>
     </row>
-    <row r="860" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -36609,7 +36609,7 @@
       <c r="AL860" s="3"/>
       <c r="AM860" s="3"/>
     </row>
-    <row r="861" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -36650,7 +36650,7 @@
       <c r="AL861" s="3"/>
       <c r="AM861" s="3"/>
     </row>
-    <row r="862" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -36691,7 +36691,7 @@
       <c r="AL862" s="3"/>
       <c r="AM862" s="3"/>
     </row>
-    <row r="863" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -36732,7 +36732,7 @@
       <c r="AL863" s="3"/>
       <c r="AM863" s="3"/>
     </row>
-    <row r="864" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -36773,7 +36773,7 @@
       <c r="AL864" s="3"/>
       <c r="AM864" s="3"/>
     </row>
-    <row r="865" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -36814,7 +36814,7 @@
       <c r="AL865" s="3"/>
       <c r="AM865" s="3"/>
     </row>
-    <row r="866" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -36855,7 +36855,7 @@
       <c r="AL866" s="3"/>
       <c r="AM866" s="3"/>
     </row>
-    <row r="867" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -36896,7 +36896,7 @@
       <c r="AL867" s="3"/>
       <c r="AM867" s="3"/>
     </row>
-    <row r="868" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -36937,7 +36937,7 @@
       <c r="AL868" s="3"/>
       <c r="AM868" s="3"/>
     </row>
-    <row r="869" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -36978,7 +36978,7 @@
       <c r="AL869" s="3"/>
       <c r="AM869" s="3"/>
     </row>
-    <row r="870" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -37019,7 +37019,7 @@
       <c r="AL870" s="3"/>
       <c r="AM870" s="3"/>
     </row>
-    <row r="871" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -37060,7 +37060,7 @@
       <c r="AL871" s="3"/>
       <c r="AM871" s="3"/>
     </row>
-    <row r="872" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -37101,7 +37101,7 @@
       <c r="AL872" s="3"/>
       <c r="AM872" s="3"/>
     </row>
-    <row r="873" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -37142,7 +37142,7 @@
       <c r="AL873" s="3"/>
       <c r="AM873" s="3"/>
     </row>
-    <row r="874" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -37183,7 +37183,7 @@
       <c r="AL874" s="3"/>
       <c r="AM874" s="3"/>
     </row>
-    <row r="875" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -37224,7 +37224,7 @@
       <c r="AL875" s="3"/>
       <c r="AM875" s="3"/>
     </row>
-    <row r="876" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -37265,7 +37265,7 @@
       <c r="AL876" s="3"/>
       <c r="AM876" s="3"/>
     </row>
-    <row r="877" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -37306,7 +37306,7 @@
       <c r="AL877" s="3"/>
       <c r="AM877" s="3"/>
     </row>
-    <row r="878" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -37347,7 +37347,7 @@
       <c r="AL878" s="3"/>
       <c r="AM878" s="3"/>
     </row>
-    <row r="879" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -37388,7 +37388,7 @@
       <c r="AL879" s="3"/>
       <c r="AM879" s="3"/>
     </row>
-    <row r="880" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -37429,7 +37429,7 @@
       <c r="AL880" s="3"/>
       <c r="AM880" s="3"/>
     </row>
-    <row r="881" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -37470,7 +37470,7 @@
       <c r="AL881" s="3"/>
       <c r="AM881" s="3"/>
     </row>
-    <row r="882" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -37511,7 +37511,7 @@
       <c r="AL882" s="3"/>
       <c r="AM882" s="3"/>
     </row>
-    <row r="883" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -37552,7 +37552,7 @@
       <c r="AL883" s="3"/>
       <c r="AM883" s="3"/>
     </row>
-    <row r="884" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -37593,7 +37593,7 @@
       <c r="AL884" s="3"/>
       <c r="AM884" s="3"/>
     </row>
-    <row r="885" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -37634,7 +37634,7 @@
       <c r="AL885" s="3"/>
       <c r="AM885" s="3"/>
     </row>
-    <row r="886" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -37675,7 +37675,7 @@
       <c r="AL886" s="3"/>
       <c r="AM886" s="3"/>
     </row>
-    <row r="887" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -37716,7 +37716,7 @@
       <c r="AL887" s="3"/>
       <c r="AM887" s="3"/>
     </row>
-    <row r="888" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -37757,7 +37757,7 @@
       <c r="AL888" s="3"/>
       <c r="AM888" s="3"/>
     </row>
-    <row r="889" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -37798,7 +37798,7 @@
       <c r="AL889" s="3"/>
       <c r="AM889" s="3"/>
     </row>
-    <row r="890" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -37839,7 +37839,7 @@
       <c r="AL890" s="3"/>
       <c r="AM890" s="3"/>
     </row>
-    <row r="891" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -37880,7 +37880,7 @@
       <c r="AL891" s="3"/>
       <c r="AM891" s="3"/>
     </row>
-    <row r="892" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -37921,7 +37921,7 @@
       <c r="AL892" s="3"/>
       <c r="AM892" s="3"/>
     </row>
-    <row r="893" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -37962,7 +37962,7 @@
       <c r="AL893" s="3"/>
       <c r="AM893" s="3"/>
     </row>
-    <row r="894" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -38003,7 +38003,7 @@
       <c r="AL894" s="3"/>
       <c r="AM894" s="3"/>
     </row>
-    <row r="895" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -38044,7 +38044,7 @@
       <c r="AL895" s="3"/>
       <c r="AM895" s="3"/>
     </row>
-    <row r="896" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -38085,7 +38085,7 @@
       <c r="AL896" s="3"/>
       <c r="AM896" s="3"/>
     </row>
-    <row r="897" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -38126,7 +38126,7 @@
       <c r="AL897" s="3"/>
       <c r="AM897" s="3"/>
     </row>
-    <row r="898" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -38167,7 +38167,7 @@
       <c r="AL898" s="3"/>
       <c r="AM898" s="3"/>
     </row>
-    <row r="899" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -38208,7 +38208,7 @@
       <c r="AL899" s="3"/>
       <c r="AM899" s="3"/>
     </row>
-    <row r="900" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -38249,7 +38249,7 @@
       <c r="AL900" s="3"/>
       <c r="AM900" s="3"/>
     </row>
-    <row r="901" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -38290,7 +38290,7 @@
       <c r="AL901" s="3"/>
       <c r="AM901" s="3"/>
     </row>
-    <row r="902" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -38331,7 +38331,7 @@
       <c r="AL902" s="3"/>
       <c r="AM902" s="3"/>
     </row>
-    <row r="903" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -38372,7 +38372,7 @@
       <c r="AL903" s="3"/>
       <c r="AM903" s="3"/>
     </row>
-    <row r="904" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -38413,7 +38413,7 @@
       <c r="AL904" s="3"/>
       <c r="AM904" s="3"/>
     </row>
-    <row r="905" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -38454,7 +38454,7 @@
       <c r="AL905" s="3"/>
       <c r="AM905" s="3"/>
     </row>
-    <row r="906" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -38495,7 +38495,7 @@
       <c r="AL906" s="3"/>
       <c r="AM906" s="3"/>
     </row>
-    <row r="907" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -38536,7 +38536,7 @@
       <c r="AL907" s="3"/>
       <c r="AM907" s="3"/>
     </row>
-    <row r="908" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -38577,7 +38577,7 @@
       <c r="AL908" s="3"/>
       <c r="AM908" s="3"/>
     </row>
-    <row r="909" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -38618,7 +38618,7 @@
       <c r="AL909" s="3"/>
       <c r="AM909" s="3"/>
     </row>
-    <row r="910" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -38659,7 +38659,7 @@
       <c r="AL910" s="3"/>
       <c r="AM910" s="3"/>
     </row>
-    <row r="911" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -38700,7 +38700,7 @@
       <c r="AL911" s="3"/>
       <c r="AM911" s="3"/>
     </row>
-    <row r="912" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -38741,7 +38741,7 @@
       <c r="AL912" s="3"/>
       <c r="AM912" s="3"/>
     </row>
-    <row r="913" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -38782,7 +38782,7 @@
       <c r="AL913" s="3"/>
       <c r="AM913" s="3"/>
     </row>
-    <row r="914" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -38823,7 +38823,7 @@
       <c r="AL914" s="3"/>
       <c r="AM914" s="3"/>
     </row>
-    <row r="915" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -38864,7 +38864,7 @@
       <c r="AL915" s="3"/>
       <c r="AM915" s="3"/>
     </row>
-    <row r="916" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -38905,7 +38905,7 @@
       <c r="AL916" s="3"/>
       <c r="AM916" s="3"/>
     </row>
-    <row r="917" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -38946,7 +38946,7 @@
       <c r="AL917" s="3"/>
       <c r="AM917" s="3"/>
     </row>
-    <row r="918" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -38987,7 +38987,7 @@
       <c r="AL918" s="3"/>
       <c r="AM918" s="3"/>
     </row>
-    <row r="919" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -39028,7 +39028,7 @@
       <c r="AL919" s="3"/>
       <c r="AM919" s="3"/>
     </row>
-    <row r="920" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -39069,7 +39069,7 @@
       <c r="AL920" s="3"/>
       <c r="AM920" s="3"/>
     </row>
-    <row r="921" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -39110,7 +39110,7 @@
       <c r="AL921" s="3"/>
       <c r="AM921" s="3"/>
     </row>
-    <row r="922" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -39151,7 +39151,7 @@
       <c r="AL922" s="3"/>
       <c r="AM922" s="3"/>
     </row>
-    <row r="923" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -39192,7 +39192,7 @@
       <c r="AL923" s="3"/>
       <c r="AM923" s="3"/>
     </row>
-    <row r="924" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -39233,7 +39233,7 @@
       <c r="AL924" s="3"/>
       <c r="AM924" s="3"/>
     </row>
-    <row r="925" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -39274,7 +39274,7 @@
       <c r="AL925" s="3"/>
       <c r="AM925" s="3"/>
     </row>
-    <row r="926" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -39315,7 +39315,7 @@
       <c r="AL926" s="3"/>
       <c r="AM926" s="3"/>
     </row>
-    <row r="927" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -39356,7 +39356,7 @@
       <c r="AL927" s="3"/>
       <c r="AM927" s="3"/>
     </row>
-    <row r="928" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -39397,7 +39397,7 @@
       <c r="AL928" s="3"/>
       <c r="AM928" s="3"/>
     </row>
-    <row r="929" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -39438,7 +39438,7 @@
       <c r="AL929" s="3"/>
       <c r="AM929" s="3"/>
     </row>
-    <row r="930" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -39479,7 +39479,7 @@
       <c r="AL930" s="3"/>
       <c r="AM930" s="3"/>
     </row>
-    <row r="931" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -39520,7 +39520,7 @@
       <c r="AL931" s="3"/>
       <c r="AM931" s="3"/>
     </row>
-    <row r="932" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -39561,7 +39561,7 @@
       <c r="AL932" s="3"/>
       <c r="AM932" s="3"/>
     </row>
-    <row r="933" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -39602,7 +39602,7 @@
       <c r="AL933" s="3"/>
       <c r="AM933" s="3"/>
     </row>
-    <row r="934" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -39643,7 +39643,7 @@
       <c r="AL934" s="3"/>
       <c r="AM934" s="3"/>
     </row>
-    <row r="935" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -39684,7 +39684,7 @@
       <c r="AL935" s="3"/>
       <c r="AM935" s="3"/>
     </row>
-    <row r="936" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -39725,7 +39725,7 @@
       <c r="AL936" s="3"/>
       <c r="AM936" s="3"/>
     </row>
-    <row r="937" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -39766,7 +39766,7 @@
       <c r="AL937" s="3"/>
       <c r="AM937" s="3"/>
     </row>
-    <row r="938" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -39807,7 +39807,7 @@
       <c r="AL938" s="3"/>
       <c r="AM938" s="3"/>
     </row>
-    <row r="939" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -39848,7 +39848,7 @@
       <c r="AL939" s="3"/>
       <c r="AM939" s="3"/>
     </row>
-    <row r="940" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -39889,7 +39889,7 @@
       <c r="AL940" s="3"/>
       <c r="AM940" s="3"/>
     </row>
-    <row r="941" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -39930,7 +39930,7 @@
       <c r="AL941" s="3"/>
       <c r="AM941" s="3"/>
     </row>
-    <row r="942" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -39971,7 +39971,7 @@
       <c r="AL942" s="3"/>
       <c r="AM942" s="3"/>
     </row>
-    <row r="943" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -40012,7 +40012,7 @@
       <c r="AL943" s="3"/>
       <c r="AM943" s="3"/>
     </row>
-    <row r="944" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -40053,7 +40053,7 @@
       <c r="AL944" s="3"/>
       <c r="AM944" s="3"/>
     </row>
-    <row r="945" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -40094,7 +40094,7 @@
       <c r="AL945" s="3"/>
       <c r="AM945" s="3"/>
     </row>
-    <row r="946" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -40135,7 +40135,7 @@
       <c r="AL946" s="3"/>
       <c r="AM946" s="3"/>
     </row>
-    <row r="947" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -40176,7 +40176,7 @@
       <c r="AL947" s="3"/>
       <c r="AM947" s="3"/>
     </row>
-    <row r="948" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -40217,7 +40217,7 @@
       <c r="AL948" s="3"/>
       <c r="AM948" s="3"/>
     </row>
-    <row r="949" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -40258,7 +40258,7 @@
       <c r="AL949" s="3"/>
       <c r="AM949" s="3"/>
     </row>
-    <row r="950" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -40299,7 +40299,7 @@
       <c r="AL950" s="3"/>
       <c r="AM950" s="3"/>
     </row>
-    <row r="951" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -40340,7 +40340,7 @@
       <c r="AL951" s="3"/>
       <c r="AM951" s="3"/>
     </row>
-    <row r="952" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -40381,7 +40381,7 @@
       <c r="AL952" s="3"/>
       <c r="AM952" s="3"/>
     </row>
-    <row r="953" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -40422,7 +40422,7 @@
       <c r="AL953" s="3"/>
       <c r="AM953" s="3"/>
     </row>
-    <row r="954" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -40463,7 +40463,7 @@
       <c r="AL954" s="3"/>
       <c r="AM954" s="3"/>
     </row>
-    <row r="955" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A955" s="3"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
@@ -40504,7 +40504,7 @@
       <c r="AL955" s="3"/>
       <c r="AM955" s="3"/>
     </row>
-    <row r="956" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A956" s="3"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
@@ -40545,7 +40545,7 @@
       <c r="AL956" s="3"/>
       <c r="AM956" s="3"/>
     </row>
-    <row r="957" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A957" s="3"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
@@ -40586,7 +40586,7 @@
       <c r="AL957" s="3"/>
       <c r="AM957" s="3"/>
     </row>
-    <row r="958" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A958" s="3"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
@@ -40627,7 +40627,7 @@
       <c r="AL958" s="3"/>
       <c r="AM958" s="3"/>
     </row>
-    <row r="959" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A959" s="3"/>
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
@@ -40668,7 +40668,7 @@
       <c r="AL959" s="3"/>
       <c r="AM959" s="3"/>
     </row>
-    <row r="960" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A960" s="3"/>
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
@@ -40709,7 +40709,7 @@
       <c r="AL960" s="3"/>
       <c r="AM960" s="3"/>
     </row>
-    <row r="961" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A961" s="3"/>
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
@@ -40750,7 +40750,7 @@
       <c r="AL961" s="3"/>
       <c r="AM961" s="3"/>
     </row>
-    <row r="962" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A962" s="3"/>
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
@@ -40791,7 +40791,7 @@
       <c r="AL962" s="3"/>
       <c r="AM962" s="3"/>
     </row>
-    <row r="963" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A963" s="3"/>
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
@@ -40832,7 +40832,7 @@
       <c r="AL963" s="3"/>
       <c r="AM963" s="3"/>
     </row>
-    <row r="964" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A964" s="3"/>
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
@@ -40873,7 +40873,7 @@
       <c r="AL964" s="3"/>
       <c r="AM964" s="3"/>
     </row>
-    <row r="965" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A965" s="3"/>
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
@@ -40914,7 +40914,7 @@
       <c r="AL965" s="3"/>
       <c r="AM965" s="3"/>
     </row>
-    <row r="966" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A966" s="3"/>
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
@@ -40955,7 +40955,7 @@
       <c r="AL966" s="3"/>
       <c r="AM966" s="3"/>
     </row>
-    <row r="967" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A967" s="3"/>
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
@@ -40996,7 +40996,7 @@
       <c r="AL967" s="3"/>
       <c r="AM967" s="3"/>
     </row>
-    <row r="968" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A968" s="3"/>
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
@@ -41037,7 +41037,7 @@
       <c r="AL968" s="3"/>
       <c r="AM968" s="3"/>
     </row>
-    <row r="969" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A969" s="3"/>
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
@@ -41078,7 +41078,7 @@
       <c r="AL969" s="3"/>
       <c r="AM969" s="3"/>
     </row>
-    <row r="970" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A970" s="3"/>
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
@@ -41119,7 +41119,7 @@
       <c r="AL970" s="3"/>
       <c r="AM970" s="3"/>
     </row>
-    <row r="971" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A971" s="3"/>
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
@@ -41160,7 +41160,7 @@
       <c r="AL971" s="3"/>
       <c r="AM971" s="3"/>
     </row>
-    <row r="972" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A972" s="3"/>
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
@@ -41201,7 +41201,7 @@
       <c r="AL972" s="3"/>
       <c r="AM972" s="3"/>
     </row>
-    <row r="973" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A973" s="3"/>
       <c r="B973" s="3"/>
       <c r="C973" s="3"/>
@@ -41242,7 +41242,7 @@
       <c r="AL973" s="3"/>
       <c r="AM973" s="3"/>
     </row>
-    <row r="974" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A974" s="3"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
@@ -41283,7 +41283,7 @@
       <c r="AL974" s="3"/>
       <c r="AM974" s="3"/>
     </row>
-    <row r="975" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A975" s="3"/>
       <c r="B975" s="3"/>
       <c r="C975" s="3"/>
@@ -41324,7 +41324,7 @@
       <c r="AL975" s="3"/>
       <c r="AM975" s="3"/>
     </row>
-    <row r="976" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A976" s="3"/>
       <c r="B976" s="3"/>
       <c r="C976" s="3"/>
@@ -41365,7 +41365,7 @@
       <c r="AL976" s="3"/>
       <c r="AM976" s="3"/>
     </row>
-    <row r="977" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A977" s="3"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
@@ -41406,7 +41406,7 @@
       <c r="AL977" s="3"/>
       <c r="AM977" s="3"/>
     </row>
-    <row r="978" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A978" s="3"/>
       <c r="B978" s="3"/>
       <c r="C978" s="3"/>
@@ -41447,7 +41447,7 @@
       <c r="AL978" s="3"/>
       <c r="AM978" s="3"/>
     </row>
-    <row r="979" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A979" s="3"/>
       <c r="B979" s="3"/>
       <c r="C979" s="3"/>
@@ -41488,7 +41488,7 @@
       <c r="AL979" s="3"/>
       <c r="AM979" s="3"/>
     </row>
-    <row r="980" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A980" s="3"/>
       <c r="B980" s="3"/>
       <c r="C980" s="3"/>
@@ -41529,7 +41529,7 @@
       <c r="AL980" s="3"/>
       <c r="AM980" s="3"/>
     </row>
-    <row r="981" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A981" s="3"/>
       <c r="B981" s="3"/>
       <c r="C981" s="3"/>
@@ -41570,7 +41570,7 @@
       <c r="AL981" s="3"/>
       <c r="AM981" s="3"/>
     </row>
-    <row r="982" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A982" s="3"/>
       <c r="B982" s="3"/>
       <c r="C982" s="3"/>
@@ -41611,7 +41611,7 @@
       <c r="AL982" s="3"/>
       <c r="AM982" s="3"/>
     </row>
-    <row r="983" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A983" s="3"/>
       <c r="B983" s="3"/>
       <c r="C983" s="3"/>
@@ -41652,7 +41652,7 @@
       <c r="AL983" s="3"/>
       <c r="AM983" s="3"/>
     </row>
-    <row r="984" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A984" s="3"/>
       <c r="B984" s="3"/>
       <c r="C984" s="3"/>
@@ -41693,7 +41693,7 @@
       <c r="AL984" s="3"/>
       <c r="AM984" s="3"/>
     </row>
-    <row r="985" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A985" s="3"/>
       <c r="B985" s="3"/>
       <c r="C985" s="3"/>
@@ -41734,7 +41734,7 @@
       <c r="AL985" s="3"/>
       <c r="AM985" s="3"/>
     </row>
-    <row r="986" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A986" s="3"/>
       <c r="B986" s="3"/>
       <c r="C986" s="3"/>
@@ -41775,7 +41775,7 @@
       <c r="AL986" s="3"/>
       <c r="AM986" s="3"/>
     </row>
-    <row r="987" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A987" s="3"/>
       <c r="B987" s="3"/>
       <c r="C987" s="3"/>
@@ -41816,7 +41816,7 @@
       <c r="AL987" s="3"/>
       <c r="AM987" s="3"/>
     </row>
-    <row r="988" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A988" s="3"/>
       <c r="B988" s="3"/>
       <c r="C988" s="3"/>
@@ -41857,7 +41857,7 @@
       <c r="AL988" s="3"/>
       <c r="AM988" s="3"/>
     </row>
-    <row r="989" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A989" s="3"/>
       <c r="B989" s="3"/>
       <c r="C989" s="3"/>
@@ -41898,7 +41898,7 @@
       <c r="AL989" s="3"/>
       <c r="AM989" s="3"/>
     </row>
-    <row r="990" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A990" s="3"/>
       <c r="B990" s="3"/>
       <c r="C990" s="3"/>
@@ -41939,7 +41939,7 @@
       <c r="AL990" s="3"/>
       <c r="AM990" s="3"/>
     </row>
-    <row r="991" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A991" s="3"/>
       <c r="B991" s="3"/>
       <c r="C991" s="3"/>
@@ -41980,7 +41980,7 @@
       <c r="AL991" s="3"/>
       <c r="AM991" s="3"/>
     </row>
-    <row r="992" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A992" s="3"/>
       <c r="B992" s="3"/>
       <c r="C992" s="3"/>
@@ -42021,7 +42021,7 @@
       <c r="AL992" s="3"/>
       <c r="AM992" s="3"/>
     </row>
-    <row r="993" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A993" s="3"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
@@ -42062,7 +42062,7 @@
       <c r="AL993" s="3"/>
       <c r="AM993" s="3"/>
     </row>
-    <row r="994" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A994" s="3"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
@@ -42103,7 +42103,7 @@
       <c r="AL994" s="3"/>
       <c r="AM994" s="3"/>
     </row>
-    <row r="995" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A995" s="3"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
@@ -42144,7 +42144,7 @@
       <c r="AL995" s="3"/>
       <c r="AM995" s="3"/>
     </row>
-    <row r="996" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A996" s="3"/>
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
@@ -42185,7 +42185,7 @@
       <c r="AL996" s="3"/>
       <c r="AM996" s="3"/>
     </row>
-    <row r="997" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A997" s="3"/>
       <c r="B997" s="3"/>
       <c r="C997" s="3"/>
@@ -42226,7 +42226,7 @@
       <c r="AL997" s="3"/>
       <c r="AM997" s="3"/>
     </row>
-    <row r="998" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A998" s="3"/>
       <c r="B998" s="3"/>
       <c r="C998" s="3"/>
@@ -42267,7 +42267,7 @@
       <c r="AL998" s="3"/>
       <c r="AM998" s="3"/>
     </row>
-    <row r="999" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A999" s="3"/>
       <c r="B999" s="3"/>
       <c r="C999" s="3"/>
@@ -42308,7 +42308,7 @@
       <c r="AL999" s="3"/>
       <c r="AM999" s="3"/>
     </row>
-    <row r="1000" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AI1000" s="3"/>
       <c r="AJ1000" s="3"/>
       <c r="AK1000" s="3"/>
@@ -42325,12 +42325,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FD7D29C8E3DCB740B512085BDB890A19" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="252040482c07e84078604bad08e1f478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1998147e-1bae-4425-a5b5-824e2b69f76d" xmlns:ns3="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a426bac492543af192e091bebadc75c6" ns2:_="" ns3:_="">
     <xsd:import namespace="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
@@ -42547,6 +42541,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -42557,23 +42557,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D20EFE-128A-4BEA-B77D-8F21601543E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42592,6 +42575,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}">
   <ds:schemaRefs>
